--- a/data/umr/Resumen UMR Abril 2026.xlsx
+++ b/data/umr/Resumen UMR Abril 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="23" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2B1165C-A4EB-425C-8C3C-E13A70A48AF2}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E21B53-FD77-490E-A880-70C8D9E435DB}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="1710" windowWidth="13935" windowHeight="9375" tabRatio="686" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -4472,14 +4472,24 @@
     <xf numFmtId="4" fontId="0" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4488,6 +4498,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4503,6 +4531,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4529,27 +4560,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4562,6 +4572,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4589,19 +4602,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -5529,37 +5529,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="343" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="343"/>
-      <c r="C1" s="343"/>
-      <c r="D1" s="343"/>
-      <c r="E1" s="343"/>
-      <c r="F1" s="343"/>
-      <c r="G1" s="343"/>
-      <c r="H1" s="343"/>
-      <c r="I1" s="343"/>
-      <c r="J1" s="343"/>
-      <c r="K1" s="343"/>
-      <c r="L1" s="343"/>
-      <c r="M1" s="343"/>
-      <c r="N1" s="343"/>
-      <c r="O1" s="343"/>
-      <c r="P1" s="343"/>
-      <c r="Q1" s="343"/>
-      <c r="R1" s="343"/>
-      <c r="S1" s="343"/>
-      <c r="T1" s="343"/>
-      <c r="U1" s="343"/>
-      <c r="V1" s="343"/>
-      <c r="W1" s="343"/>
-      <c r="X1" s="343"/>
-      <c r="Y1" s="343"/>
-      <c r="Z1" s="343"/>
-      <c r="AA1" s="343"/>
-      <c r="AB1" s="343"/>
-      <c r="AC1" s="343"/>
+      <c r="A1" s="347" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="347"/>
+      <c r="C1" s="347"/>
+      <c r="D1" s="347"/>
+      <c r="E1" s="347"/>
+      <c r="F1" s="347"/>
+      <c r="G1" s="347"/>
+      <c r="H1" s="347"/>
+      <c r="I1" s="347"/>
+      <c r="J1" s="347"/>
+      <c r="K1" s="347"/>
+      <c r="L1" s="347"/>
+      <c r="M1" s="347"/>
+      <c r="N1" s="347"/>
+      <c r="O1" s="347"/>
+      <c r="P1" s="347"/>
+      <c r="Q1" s="347"/>
+      <c r="R1" s="347"/>
+      <c r="S1" s="347"/>
+      <c r="T1" s="347"/>
+      <c r="U1" s="347"/>
+      <c r="V1" s="347"/>
+      <c r="W1" s="347"/>
+      <c r="X1" s="347"/>
+      <c r="Y1" s="347"/>
+      <c r="Z1" s="347"/>
+      <c r="AA1" s="347"/>
+      <c r="AB1" s="347"/>
+      <c r="AC1" s="347"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -9704,37 +9704,37 @@
       <c r="AC46" s="212"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="343" t="s">
+      <c r="A47" s="347" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="343"/>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-      <c r="G47" s="343"/>
-      <c r="H47" s="343"/>
-      <c r="I47" s="343"/>
-      <c r="J47" s="343"/>
-      <c r="K47" s="343"/>
-      <c r="L47" s="343"/>
-      <c r="M47" s="343"/>
-      <c r="N47" s="343"/>
-      <c r="O47" s="343"/>
-      <c r="P47" s="343"/>
-      <c r="Q47" s="343"/>
-      <c r="R47" s="343"/>
-      <c r="S47" s="343"/>
-      <c r="T47" s="343"/>
-      <c r="U47" s="343"/>
-      <c r="V47" s="343"/>
-      <c r="W47" s="343"/>
-      <c r="X47" s="343"/>
-      <c r="Y47" s="343"/>
-      <c r="Z47" s="343"/>
-      <c r="AA47" s="343"/>
-      <c r="AB47" s="343"/>
-      <c r="AC47" s="343"/>
+      <c r="B47" s="347"/>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+      <c r="G47" s="347"/>
+      <c r="H47" s="347"/>
+      <c r="I47" s="347"/>
+      <c r="J47" s="347"/>
+      <c r="K47" s="347"/>
+      <c r="L47" s="347"/>
+      <c r="M47" s="347"/>
+      <c r="N47" s="347"/>
+      <c r="O47" s="347"/>
+      <c r="P47" s="347"/>
+      <c r="Q47" s="347"/>
+      <c r="R47" s="347"/>
+      <c r="S47" s="347"/>
+      <c r="T47" s="347"/>
+      <c r="U47" s="347"/>
+      <c r="V47" s="347"/>
+      <c r="W47" s="347"/>
+      <c r="X47" s="347"/>
+      <c r="Y47" s="347"/>
+      <c r="Z47" s="347"/>
+      <c r="AA47" s="347"/>
+      <c r="AB47" s="347"/>
+      <c r="AC47" s="347"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -14793,122 +14793,122 @@
       <c r="A91" s="330" t="s">
         <v>177</v>
       </c>
-      <c r="B91" s="383">
-        <v>0</v>
-      </c>
-      <c r="C91" s="383">
+      <c r="B91" s="343">
+        <v>0</v>
+      </c>
+      <c r="C91" s="343">
         <f>C43-B43</f>
         <v>0</v>
       </c>
-      <c r="D91" s="383">
+      <c r="D91" s="343">
         <f t="shared" ref="D91:H91" si="81">D43-C43</f>
         <v>0</v>
       </c>
-      <c r="E91" s="383">
+      <c r="E91" s="343">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="F91" s="383">
+      <c r="F91" s="343">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="G91" s="383">
+      <c r="G91" s="343">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="H91" s="383">
+      <c r="H91" s="343">
         <f t="shared" si="81"/>
         <v>19</v>
       </c>
-      <c r="I91" s="383">
+      <c r="I91" s="343">
         <f>H43-G43</f>
         <v>19</v>
       </c>
-      <c r="J91" s="383">
+      <c r="J91" s="343">
         <f t="shared" ref="J91:K91" si="82">I43-H43</f>
         <v>0</v>
       </c>
-      <c r="K91" s="383">
+      <c r="K91" s="343">
         <f t="shared" si="82"/>
         <v>44</v>
       </c>
-      <c r="L91" s="383">
+      <c r="L91" s="343">
         <f t="shared" ref="L91" si="83">L43-K43</f>
         <v>0</v>
       </c>
-      <c r="M91" s="383">
+      <c r="M91" s="343">
         <f t="shared" ref="M91" si="84">M43-L43</f>
         <v>46</v>
       </c>
-      <c r="N91" s="383">
+      <c r="N91" s="343">
         <f t="shared" ref="N91" si="85">N43-M43</f>
         <v>128</v>
       </c>
-      <c r="O91" s="383">
+      <c r="O91" s="343">
         <f t="shared" ref="O91" si="86">O43-N43</f>
         <v>0</v>
       </c>
-      <c r="P91" s="383">
+      <c r="P91" s="343">
         <f t="shared" ref="P91" si="87">P43-O43</f>
         <v>86</v>
       </c>
-      <c r="Q91" s="383">
+      <c r="Q91" s="343">
         <f t="shared" ref="Q91" si="88">Q43-P43</f>
         <v>0</v>
       </c>
-      <c r="R91" s="383">
+      <c r="R91" s="343">
         <f t="shared" ref="R91" si="89">R43-Q43</f>
         <v>94</v>
       </c>
-      <c r="S91" s="383">
+      <c r="S91" s="343">
         <f t="shared" ref="S91" si="90">S43-R43</f>
         <v>0</v>
       </c>
-      <c r="T91" s="383">
+      <c r="T91" s="343">
         <f t="shared" ref="T91" si="91">T43-S43</f>
         <v>87</v>
       </c>
-      <c r="U91" s="383">
+      <c r="U91" s="343">
         <f t="shared" ref="U91" si="92">U43-T43</f>
         <v>0</v>
       </c>
-      <c r="V91" s="383">
+      <c r="V91" s="343">
         <f t="shared" ref="V91" si="93">V43-U43</f>
         <v>86</v>
       </c>
-      <c r="W91" s="383">
+      <c r="W91" s="343">
         <f t="shared" ref="W91" si="94">W43-V43</f>
         <v>124</v>
       </c>
-      <c r="X91" s="383">
+      <c r="X91" s="343">
         <f t="shared" ref="X91" si="95">X43-W43</f>
         <v>123</v>
       </c>
-      <c r="Y91" s="383">
+      <c r="Y91" s="343">
         <f t="shared" ref="Y91" si="96">Y43-X43</f>
         <v>123</v>
       </c>
-      <c r="Z91" s="383">
+      <c r="Z91" s="343">
         <f t="shared" ref="Z91:AA91" si="97">Z43-Y43</f>
         <v>0</v>
       </c>
-      <c r="AA91" s="383">
+      <c r="AA91" s="343">
         <f t="shared" si="97"/>
         <v>0</v>
       </c>
-      <c r="AB91" s="383">
+      <c r="AB91" s="343">
         <f t="shared" si="76"/>
         <v>253</v>
       </c>
-      <c r="AC91" s="383">
+      <c r="AC91" s="343">
         <f t="shared" si="77"/>
         <v>298</v>
       </c>
-      <c r="AD91" s="383">
+      <c r="AD91" s="343">
         <f t="shared" si="78"/>
         <v>186</v>
       </c>
-      <c r="AE91" s="383">
+      <c r="AE91" s="343">
         <f t="shared" si="78"/>
         <v>165</v>
       </c>
@@ -15162,57 +15162,57 @@
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AC95" s="386">
+      <c r="AC95" s="346">
         <f>3*'KM-Servicio'!$M$1+2*4.82</f>
         <v>96.97</v>
       </c>
-      <c r="AD95" s="384">
+      <c r="AD95" s="344">
         <f>43.13+18.83</f>
         <v>61.96</v>
       </c>
-      <c r="AE95" s="384">
+      <c r="AE95" s="344">
         <f>43.13+18.83</f>
         <v>61.96</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AC96" s="386">
+      <c r="AC96" s="346">
         <f>3*'KM-Servicio'!$M$1+2*4.82</f>
         <v>96.97</v>
       </c>
-      <c r="AD96" s="384">
+      <c r="AD96" s="344">
         <f>43.13+18.83</f>
         <v>61.96</v>
       </c>
-      <c r="AE96" s="384">
+      <c r="AE96" s="344">
         <f>43.13+18.83</f>
         <v>61.96</v>
       </c>
     </row>
     <row r="97" spans="29:31" x14ac:dyDescent="0.25">
-      <c r="AC97" s="385">
+      <c r="AC97" s="345">
         <f>AC95+AC96</f>
         <v>193.94</v>
       </c>
-      <c r="AD97" s="385">
+      <c r="AD97" s="345">
         <f>AD95+AD96</f>
         <v>123.92</v>
       </c>
-      <c r="AE97" s="385">
+      <c r="AE97" s="345">
         <f>AE95+AE96</f>
         <v>123.92</v>
       </c>
     </row>
     <row r="98" spans="29:31" x14ac:dyDescent="0.25">
-      <c r="AC98" s="385">
+      <c r="AC98" s="345">
         <f>AC91-AC97</f>
         <v>104.06</v>
       </c>
-      <c r="AD98" s="385">
+      <c r="AD98" s="345">
         <f>AD91-AD97</f>
         <v>62.08</v>
       </c>
-      <c r="AE98" s="385">
+      <c r="AE98" s="345">
         <f>AE91-AE97</f>
         <v>41.08</v>
       </c>
@@ -15345,14 +15345,14 @@
     </row>
     <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="362" t="s">
+      <c r="B2" s="357" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="362"/>
-      <c r="D2" s="363" t="s">
+      <c r="C2" s="357"/>
+      <c r="D2" s="358" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="363"/>
+      <c r="E2" s="358"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15430,59 +15430,59 @@
     </row>
     <row r="3" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="362" t="s">
+      <c r="B3" s="357" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="362"/>
-      <c r="D3" s="363" t="s">
+      <c r="C3" s="357"/>
+      <c r="D3" s="358" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="363"/>
-      <c r="F3" s="344" t="s">
+      <c r="E3" s="358"/>
+      <c r="F3" s="353" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="344" t="s">
+      <c r="G3" s="353" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="344" t="s">
+      <c r="H3" s="353" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="344" t="s">
+      <c r="I3" s="353" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="344" t="s">
+      <c r="J3" s="353" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="344" t="s">
+      <c r="K3" s="353" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="344" t="s">
+      <c r="L3" s="353" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="344" t="s">
+      <c r="M3" s="353" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="345" t="s">
+      <c r="N3" s="364" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="345" t="s">
+      <c r="O3" s="364" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="353"/>
-      <c r="Q3" s="354" t="s">
+      <c r="P3" s="363"/>
+      <c r="Q3" s="365" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="355"/>
-      <c r="S3" s="356"/>
-      <c r="T3" s="357" t="s">
+      <c r="R3" s="366"/>
+      <c r="S3" s="367"/>
+      <c r="T3" s="368" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="358"/>
-      <c r="V3" s="359"/>
-      <c r="W3" s="351" t="s">
+      <c r="U3" s="369"/>
+      <c r="V3" s="370"/>
+      <c r="W3" s="361" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="351" t="s">
+      <c r="X3" s="361" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15500,17 +15500,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="344"/>
-      <c r="G4" s="364"/>
-      <c r="H4" s="364"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="344"/>
-      <c r="N4" s="345"/>
-      <c r="O4" s="345"/>
-      <c r="P4" s="353"/>
+      <c r="F4" s="353"/>
+      <c r="G4" s="354"/>
+      <c r="H4" s="354"/>
+      <c r="I4" s="353"/>
+      <c r="J4" s="353"/>
+      <c r="K4" s="353"/>
+      <c r="L4" s="353"/>
+      <c r="M4" s="353"/>
+      <c r="N4" s="364"/>
+      <c r="O4" s="364"/>
+      <c r="P4" s="363"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15529,8 +15529,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="352"/>
-      <c r="X4" s="352"/>
+      <c r="W4" s="362"/>
+      <c r="X4" s="362"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -16055,9 +16055,7 @@
       <c r="N12" s="19"/>
       <c r="O12" s="19"/>
       <c r="P12" s="146"/>
-      <c r="Q12" s="183">
-        <v>2</v>
-      </c>
+      <c r="Q12" s="183"/>
       <c r="R12" s="183"/>
       <c r="S12" s="206"/>
       <c r="T12" s="285"/>
@@ -16065,7 +16063,7 @@
       <c r="V12" s="228"/>
       <c r="W12" s="182">
         <f>J12-(Q12*($M$2-$K$1))-(R12*($M$2-$M$1))- (S12*($M$2-$I$2))+ (T12*($G$2))</f>
-        <v>5355.79</v>
+        <v>5391.25</v>
       </c>
       <c r="X12" s="182">
         <f>H12*$M$2</f>
@@ -16127,13 +16125,13 @@
       <c r="R13" s="186"/>
       <c r="S13" s="217"/>
       <c r="T13" s="183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U13" s="217"/>
       <c r="V13" s="229"/>
       <c r="W13" s="185">
         <f>J13-(T13*($M$2-$K$1)+(U13*($M$2-$M$1)))</f>
-        <v>5320.33</v>
+        <v>5338.06</v>
       </c>
       <c r="X13" s="182">
         <f>H13*$M$2</f>
@@ -16191,9 +16189,7 @@
       <c r="N14" s="19"/>
       <c r="O14" s="19"/>
       <c r="P14" s="146"/>
-      <c r="Q14" s="244">
-        <v>2</v>
-      </c>
+      <c r="Q14" s="244"/>
       <c r="R14" s="190"/>
       <c r="S14" s="228"/>
       <c r="T14" s="186"/>
@@ -16201,7 +16197,7 @@
       <c r="V14" s="189"/>
       <c r="W14" s="182">
         <f>J14-(Q14*($M$1-$K$1))</f>
-        <v>1098.76</v>
+        <v>1106.18</v>
       </c>
       <c r="X14" s="182">
         <f>H14*$M$1</f>
@@ -16457,7 +16453,7 @@
       </c>
       <c r="O18" s="21">
         <f>(W18/N18)*100</f>
-        <v>96.102629220197187</v>
+        <v>96.555348072901111</v>
       </c>
       <c r="P18" s="192"/>
       <c r="Q18" s="181"/>
@@ -16468,7 +16464,7 @@
       <c r="V18" s="181"/>
       <c r="W18" s="193">
         <f>SUM(W12:W17)</f>
-        <v>12866.22</v>
+        <v>12926.830000000002</v>
       </c>
       <c r="X18" s="193">
         <f>SUM(X12:X17)</f>
@@ -16544,7 +16540,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="367" t="s">
+      <c r="A20" s="355" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="218">
@@ -16611,7 +16607,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="367"/>
+      <c r="A21" s="355"/>
       <c r="B21" s="218">
         <v>0</v>
       </c>
@@ -16676,7 +16672,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="367"/>
+      <c r="A22" s="355"/>
       <c r="B22" s="218">
         <v>0</v>
       </c>
@@ -16741,7 +16737,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="367"/>
+      <c r="A23" s="355"/>
       <c r="B23" s="218">
         <v>0</v>
       </c>
@@ -16806,7 +16802,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="367"/>
+      <c r="A24" s="355"/>
       <c r="B24" s="218">
         <v>0</v>
       </c>
@@ -17010,7 +17006,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="367" t="s">
+      <c r="A27" s="355" t="s">
         <v>181</v>
       </c>
       <c r="B27" s="218">
@@ -17077,7 +17073,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="367"/>
+      <c r="A28" s="355"/>
       <c r="B28" s="218">
         <v>0</v>
       </c>
@@ -17142,7 +17138,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="367"/>
+      <c r="A29" s="355"/>
       <c r="B29" s="218">
         <v>0</v>
       </c>
@@ -17207,7 +17203,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="367"/>
+      <c r="A30" s="355"/>
       <c r="B30" s="218">
         <v>0</v>
       </c>
@@ -17271,7 +17267,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="367"/>
+      <c r="A31" s="355"/>
       <c r="B31" s="218">
         <v>0</v>
       </c>
@@ -17940,7 +17936,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="368" t="s">
+      <c r="A41" s="356" t="s">
         <v>182</v>
       </c>
       <c r="B41" s="295">
@@ -18009,7 +18005,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="368"/>
+      <c r="A42" s="356"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -18083,7 +18079,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="368"/>
+      <c r="A43" s="356"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -18155,7 +18151,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="368"/>
+      <c r="A44" s="356"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -18227,7 +18223,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="368"/>
+      <c r="A45" s="356"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -18924,7 +18920,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="367" t="s">
+      <c r="A55" s="355" t="s">
         <v>183</v>
       </c>
       <c r="B55" s="295">
@@ -18995,7 +18991,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="367"/>
+      <c r="A56" s="355"/>
       <c r="B56" s="295">
         <v>33</v>
       </c>
@@ -19062,7 +19058,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="367"/>
+      <c r="A57" s="355"/>
       <c r="B57" s="295">
         <v>29</v>
       </c>
@@ -19130,7 +19126,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="367"/>
+      <c r="A58" s="355"/>
       <c r="B58" s="295">
         <v>0</v>
       </c>
@@ -19195,7 +19191,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="367"/>
+      <c r="A59" s="355"/>
       <c r="B59" s="295">
         <v>4</v>
       </c>
@@ -25540,7 +25536,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="368" t="s">
+      <c r="A153" s="356" t="s">
         <v>186</v>
       </c>
       <c r="B153" s="295">
@@ -25611,7 +25607,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="368"/>
+      <c r="A154" s="356"/>
       <c r="B154" s="295">
         <v>33</v>
       </c>
@@ -25680,7 +25676,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="368"/>
+      <c r="A155" s="356"/>
       <c r="B155" s="295">
         <v>29</v>
       </c>
@@ -25747,7 +25743,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="368"/>
+      <c r="A156" s="356"/>
       <c r="B156" s="295">
         <v>0</v>
       </c>
@@ -25814,7 +25810,7 @@
       <c r="Z156" s="124"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="368"/>
+      <c r="A157" s="356"/>
       <c r="B157" s="295">
         <v>4</v>
       </c>
@@ -29909,38 +29905,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="346" t="s">
+      <c r="B223" s="350" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="347"/>
-      <c r="D223" s="347"/>
-      <c r="E223" s="347"/>
-      <c r="F223" s="347"/>
-      <c r="G223" s="348"/>
+      <c r="C223" s="351"/>
+      <c r="D223" s="351"/>
+      <c r="E223" s="351"/>
+      <c r="F223" s="351"/>
+      <c r="G223" s="352"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="346" t="s">
+      <c r="I223" s="350" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="347"/>
-      <c r="K223" s="347"/>
-      <c r="L223" s="347"/>
-      <c r="M223" s="347"/>
-      <c r="N223" s="348"/>
-      <c r="P223" s="360" t="s">
+      <c r="J223" s="351"/>
+      <c r="K223" s="351"/>
+      <c r="L223" s="351"/>
+      <c r="M223" s="351"/>
+      <c r="N223" s="352"/>
+      <c r="P223" s="371" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="360"/>
-      <c r="R223" s="360"/>
-      <c r="S223" s="361"/>
-      <c r="T223" s="357" t="s">
+      <c r="Q223" s="371"/>
+      <c r="R223" s="371"/>
+      <c r="S223" s="372"/>
+      <c r="T223" s="368" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="358"/>
-      <c r="V223" s="359"/>
-      <c r="W223" s="349" t="s">
+      <c r="U223" s="369"/>
+      <c r="V223" s="370"/>
+      <c r="W223" s="359" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="349" t="s">
+      <c r="X223" s="359" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30006,8 +30002,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="350"/>
-      <c r="X224" s="350"/>
+      <c r="W224" s="360"/>
+      <c r="X224" s="360"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30065,7 +30061,7 @@
       <c r="O225" s="124"/>
       <c r="P225" s="209">
         <f>SUM(Q194,Q187,Q180,Q173,Q166,Q159,Q152,Q145,Q138,Q131,Q124,Q117,Q110,Q103,Q96,Q89,Q82,Q75,Q68,Q61,Q54,Q47,Q40,Q33,Q26,Q19,Q12,Q5,Q201,Q208,Q215)</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q225" s="209">
         <f>SUM(R194,R187,R180,R173,R166,R159,R152,R145,R138,R131,R124,R117,R110,R103,R96,R89,R82,R75,R68,R61,R54,R47,R40,R33,R26,R19,R12,R5,R201,R208,R215)</f>
@@ -30081,7 +30077,7 @@
       </c>
       <c r="T225" s="209">
         <f>SUM(T194,T187,T180,T173,T166,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T201,T208,T215)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T167+T174+T181+T188+T195+T202+T209+T216</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U225" s="209">
         <f>SUM(U194,U187,U180,U173,U166,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U201,U208,U216)</f>
@@ -30093,7 +30089,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>314258.34999999998</v>
+        <v>314318.96000000002</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -30559,10 +30555,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="365" t="s">
+      <c r="B237" s="348" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="366"/>
+      <c r="C237" s="349"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -30738,20 +30734,13 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A153:A157"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="X223:X224"/>
     <mergeCell ref="W223:W224"/>
     <mergeCell ref="W3:W4"/>
@@ -30762,13 +30751,20 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="P223:S223"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A153:A157"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D194:E199 D187:E192 D180:E185 D173:E178 D166:E171 D159:E164">
     <cfRule type="expression" dxfId="39" priority="134">
@@ -30992,126 +30988,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="369">
+      <c r="D1" s="373">
         <v>46113</v>
       </c>
-      <c r="E1" s="369"/>
-      <c r="F1" s="369">
+      <c r="E1" s="373"/>
+      <c r="F1" s="373">
         <v>46114</v>
       </c>
-      <c r="G1" s="369"/>
-      <c r="H1" s="369">
+      <c r="G1" s="373"/>
+      <c r="H1" s="373">
         <v>46115</v>
       </c>
-      <c r="I1" s="369"/>
-      <c r="J1" s="369">
+      <c r="I1" s="373"/>
+      <c r="J1" s="373">
         <v>46116</v>
       </c>
-      <c r="K1" s="369"/>
-      <c r="L1" s="369">
+      <c r="K1" s="373"/>
+      <c r="L1" s="373">
         <v>46117</v>
       </c>
-      <c r="M1" s="369"/>
-      <c r="N1" s="369">
+      <c r="M1" s="373"/>
+      <c r="N1" s="373">
         <v>46118</v>
       </c>
-      <c r="O1" s="369"/>
-      <c r="P1" s="369">
+      <c r="O1" s="373"/>
+      <c r="P1" s="373">
         <v>46119</v>
       </c>
-      <c r="Q1" s="369"/>
-      <c r="R1" s="369">
+      <c r="Q1" s="373"/>
+      <c r="R1" s="373">
         <v>46120</v>
       </c>
-      <c r="S1" s="369"/>
-      <c r="T1" s="369">
+      <c r="S1" s="373"/>
+      <c r="T1" s="373">
         <v>46121</v>
       </c>
-      <c r="U1" s="369"/>
-      <c r="V1" s="369">
+      <c r="U1" s="373"/>
+      <c r="V1" s="373">
         <v>46122</v>
       </c>
-      <c r="W1" s="369"/>
-      <c r="X1" s="369">
+      <c r="W1" s="373"/>
+      <c r="X1" s="373">
         <v>46123</v>
       </c>
-      <c r="Y1" s="369"/>
-      <c r="Z1" s="369">
+      <c r="Y1" s="373"/>
+      <c r="Z1" s="373">
         <v>46124</v>
       </c>
-      <c r="AA1" s="369"/>
-      <c r="AB1" s="369">
+      <c r="AA1" s="373"/>
+      <c r="AB1" s="373">
         <v>46125</v>
       </c>
-      <c r="AC1" s="369"/>
-      <c r="AD1" s="369">
+      <c r="AC1" s="373"/>
+      <c r="AD1" s="373">
         <v>46126</v>
       </c>
-      <c r="AE1" s="369"/>
-      <c r="AF1" s="369">
+      <c r="AE1" s="373"/>
+      <c r="AF1" s="373">
         <v>46127</v>
       </c>
-      <c r="AG1" s="369"/>
-      <c r="AH1" s="369">
+      <c r="AG1" s="373"/>
+      <c r="AH1" s="373">
         <v>46128</v>
       </c>
-      <c r="AI1" s="369"/>
-      <c r="AJ1" s="369">
+      <c r="AI1" s="373"/>
+      <c r="AJ1" s="373">
         <v>46129</v>
       </c>
-      <c r="AK1" s="369"/>
-      <c r="AL1" s="369">
+      <c r="AK1" s="373"/>
+      <c r="AL1" s="373">
         <v>46130</v>
       </c>
-      <c r="AM1" s="369"/>
-      <c r="AN1" s="369">
+      <c r="AM1" s="373"/>
+      <c r="AN1" s="373">
         <v>46131</v>
       </c>
-      <c r="AO1" s="369"/>
-      <c r="AP1" s="369">
+      <c r="AO1" s="373"/>
+      <c r="AP1" s="373">
         <v>46132</v>
       </c>
-      <c r="AQ1" s="369"/>
-      <c r="AR1" s="369">
+      <c r="AQ1" s="373"/>
+      <c r="AR1" s="373">
         <v>46133</v>
       </c>
-      <c r="AS1" s="369"/>
-      <c r="AT1" s="369">
+      <c r="AS1" s="373"/>
+      <c r="AT1" s="373">
         <v>46134</v>
       </c>
-      <c r="AU1" s="369"/>
-      <c r="AV1" s="369">
+      <c r="AU1" s="373"/>
+      <c r="AV1" s="373">
         <v>46135</v>
       </c>
-      <c r="AW1" s="369"/>
-      <c r="AX1" s="369">
+      <c r="AW1" s="373"/>
+      <c r="AX1" s="373">
         <v>46136</v>
       </c>
-      <c r="AY1" s="369"/>
-      <c r="AZ1" s="369">
+      <c r="AY1" s="373"/>
+      <c r="AZ1" s="373">
         <v>46137</v>
       </c>
-      <c r="BA1" s="369"/>
-      <c r="BB1" s="369">
+      <c r="BA1" s="373"/>
+      <c r="BB1" s="373">
         <v>46138</v>
       </c>
-      <c r="BC1" s="369"/>
-      <c r="BD1" s="369">
+      <c r="BC1" s="373"/>
+      <c r="BD1" s="373">
         <v>46139</v>
       </c>
-      <c r="BE1" s="369"/>
-      <c r="BF1" s="369">
+      <c r="BE1" s="373"/>
+      <c r="BF1" s="373">
         <v>46140</v>
       </c>
-      <c r="BG1" s="369"/>
-      <c r="BH1" s="369">
+      <c r="BG1" s="373"/>
+      <c r="BH1" s="373">
         <v>46141</v>
       </c>
-      <c r="BI1" s="369"/>
-      <c r="BJ1" s="369">
+      <c r="BI1" s="373"/>
+      <c r="BJ1" s="373">
         <v>46142</v>
       </c>
-      <c r="BK1" s="369"/>
+      <c r="BK1" s="373"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -36877,10 +36873,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="370" t="s">
+      <c r="A37" s="374" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="370"/>
+      <c r="B37" s="374"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="13">SUM(D31:D36)</f>
@@ -39350,21 +39346,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -39381,6 +39362,21 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -41114,7 +41110,7 @@
       </c>
       <c r="D19" s="83">
         <f>'KM-Servicio'!Q12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="83">
         <f>'KM-Servicio'!Q19</f>
@@ -41242,7 +41238,7 @@
       </c>
       <c r="D20" s="83">
         <f>'KM-Servicio'!T13</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="83">
         <f>'KM-Servicio'!T20</f>
@@ -41498,7 +41494,7 @@
       </c>
       <c r="D22" s="83">
         <f>'KM-Servicio'!Q14</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="83">
         <f>'KM-Servicio'!Q21</f>
@@ -42000,7 +41996,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>314258.34999999998</v>
+        <v>314318.96000000002</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42008,7 +42004,7 @@
       </c>
       <c r="D29" s="91">
         <f>(D12*$B$12+D13*$B$13+D14*$B$14+D15*$B$15+D17*$B$17+D20*$B$20+D16*$B$16+D19*$B$19+D21*$B$21+D23*$B$23+D24*B24+D22*B22)</f>
-        <v>12866.220000000001</v>
+        <v>12926.83</v>
       </c>
       <c r="E29" s="91">
         <f>(E12*$B$12+E13*$B$13+E14*$B$14+E15*$B$15+E17*$B$17+E20*$B$20+E16*$B$16+E19*$B$19+E21*$B$21+E23*$B$23+E24*B24+E22*B22)</f>
@@ -42258,7 +42254,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32682868.400000006</v>
+        <v>32689171.840000004</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -42266,7 +42262,7 @@
       </c>
       <c r="D31" s="91">
         <f t="shared" si="12"/>
-        <v>1338086.8800000001</v>
+        <v>1344390.32</v>
       </c>
       <c r="E31" s="91">
         <f t="shared" si="12"/>
@@ -42387,7 +42383,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>628516.69999999995</v>
+        <v>628637.92000000004</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -42395,7 +42391,7 @@
       </c>
       <c r="D32" s="91">
         <f t="shared" ref="D32:AD32" si="15">D29*2</f>
-        <v>25732.440000000002</v>
+        <v>25853.66</v>
       </c>
       <c r="E32" s="91">
         <f t="shared" si="15"/>
@@ -42645,7 +42641,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24920687.155000005</v>
+        <v>24925493.528000005</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -42653,7 +42649,7 @@
       </c>
       <c r="D34" s="91">
         <f t="shared" ref="D34:AD34" si="21">D29*79.3</f>
-        <v>1020291.246</v>
+        <v>1025097.6189999999</v>
       </c>
       <c r="E34" s="91">
         <f t="shared" si="21"/>
@@ -43079,19 +43075,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="371" t="s">
+      <c r="A2" s="375" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="372"/>
-      <c r="C2" s="372"/>
-      <c r="D2" s="372"/>
-      <c r="E2" s="372"/>
-      <c r="F2" s="372"/>
-      <c r="G2" s="372"/>
-      <c r="H2" s="372"/>
-      <c r="I2" s="372"/>
-      <c r="J2" s="372"/>
-      <c r="K2" s="372"/>
+      <c r="B2" s="376"/>
+      <c r="C2" s="376"/>
+      <c r="D2" s="376"/>
+      <c r="E2" s="376"/>
+      <c r="F2" s="376"/>
+      <c r="G2" s="376"/>
+      <c r="H2" s="376"/>
+      <c r="I2" s="376"/>
+      <c r="J2" s="376"/>
+      <c r="K2" s="376"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -43184,15 +43180,15 @@
       </c>
       <c r="D5" s="341">
         <f>'KM-Servicio'!W18</f>
-        <v>12866.22</v>
+        <v>12926.830000000002</v>
       </c>
       <c r="E5" s="12">
         <f>D5+E4</f>
-        <v>25042.36</v>
+        <v>25102.97</v>
       </c>
       <c r="F5" s="166">
         <f>'KM-Servicio'!O18</f>
-        <v>96.102629220197187</v>
+        <v>96.555348072901111</v>
       </c>
       <c r="G5" s="167">
         <f>SUM('KM-Servicio'!B18:C18)</f>
@@ -43204,7 +43200,7 @@
       </c>
       <c r="I5" s="12">
         <f>'Oferta Diaria'!D34</f>
-        <v>1020291.246</v>
+        <v>1025097.6189999999</v>
       </c>
       <c r="J5" s="161" t="s">
         <v>137</v>
@@ -43230,7 +43226,7 @@
       </c>
       <c r="E6" s="12">
         <f t="shared" ref="E6:E33" si="1">D6+E5</f>
-        <v>29959.18</v>
+        <v>30019.79</v>
       </c>
       <c r="F6" s="166">
         <f>'KM-Servicio'!O25</f>
@@ -43272,7 +43268,7 @@
       </c>
       <c r="E7" s="12">
         <f t="shared" si="1"/>
-        <v>34876</v>
+        <v>34936.61</v>
       </c>
       <c r="F7" s="166">
         <f>'KM-Servicio'!O32</f>
@@ -43314,7 +43310,7 @@
       </c>
       <c r="E8" s="12">
         <f t="shared" si="1"/>
-        <v>39792.82</v>
+        <v>39853.43</v>
       </c>
       <c r="F8" s="166">
         <f>'KM-Servicio'!O39</f>
@@ -43356,7 +43352,7 @@
       </c>
       <c r="E9" s="312">
         <f t="shared" si="1"/>
-        <v>52314</v>
+        <v>52374.61</v>
       </c>
       <c r="F9" s="313">
         <f>'KM-Servicio'!O46</f>
@@ -43398,7 +43394,7 @@
       </c>
       <c r="E10" s="312">
         <f t="shared" si="1"/>
-        <v>64745.210000000006</v>
+        <v>64805.820000000007</v>
       </c>
       <c r="F10" s="313">
         <f>'KM-Servicio'!O53</f>
@@ -43440,7 +43436,7 @@
       </c>
       <c r="E11" s="312">
         <f t="shared" si="1"/>
-        <v>76854.320000000007</v>
+        <v>76914.930000000008</v>
       </c>
       <c r="F11" s="313">
         <f>'KM-Servicio'!O60</f>
@@ -43482,7 +43478,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>89426.3</v>
+        <v>89486.91</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -43524,7 +43520,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>102104.66</v>
+        <v>102165.27</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -43566,7 +43562,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>108574.16</v>
+        <v>108634.77</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -43608,7 +43604,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113490.98000000001</v>
+        <v>113551.59000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -43650,7 +43646,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>125943.63</v>
+        <v>126004.24000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O95</f>
@@ -43692,7 +43688,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138518</v>
+        <v>138578.61000000002</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O102</f>
@@ -43734,7 +43730,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151070.93</v>
+        <v>151131.54</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
@@ -43776,7 +43772,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>163716.22</v>
+        <v>163776.83000000002</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -43817,7 +43813,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>176251.42</v>
+        <v>176312.03000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -43859,7 +43855,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>182720.92</v>
+        <v>182781.53000000003</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -43901,7 +43897,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187724</v>
+        <v>187784.61000000002</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -43943,7 +43939,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>200313.71</v>
+        <v>200374.32</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O144</f>
@@ -43985,7 +43981,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>212748.63</v>
+        <v>212809.24000000002</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O151</f>
@@ -44027,7 +44023,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>225543.67999999999</v>
+        <v>225604.29</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -44069,7 +44065,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>238047.13</v>
+        <v>238107.74000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44111,7 +44107,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>250451.62</v>
+        <v>250512.23</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44153,7 +44149,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>256921.12</v>
+        <v>256981.73</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44195,7 +44191,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>261837.94</v>
+        <v>261898.55000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44237,7 +44233,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>274820.59999999998</v>
+        <v>274881.21000000002</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44279,7 +44275,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>289233.71999999997</v>
+        <v>289294.33</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44321,7 +44317,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>301737.17</v>
+        <v>301797.78000000003</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44363,7 +44359,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>314258.34999999998</v>
+        <v>314318.96000000002</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44435,15 +44431,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>314258.34999999998</v>
+        <v>314318.96000000002</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4701214.92</v>
+        <v>4702972.6100000003</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.21497649533498</v>
+        <v>97.23006712375846</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44455,7 +44451,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24920687.155000005</v>
+        <v>24925493.528000005</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -44490,12 +44486,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="373" t="s">
+      <c r="A3" s="378" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="374"/>
-      <c r="C3" s="374"/>
-      <c r="D3" s="375"/>
+      <c r="B3" s="379"/>
+      <c r="C3" s="379"/>
+      <c r="D3" s="380"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44641,12 +44637,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="376" t="s">
+      <c r="A13" s="381" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="377"/>
-      <c r="C13" s="377"/>
-      <c r="D13" s="378"/>
+      <c r="B13" s="382"/>
+      <c r="C13" s="382"/>
+      <c r="D13" s="383"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -44693,8 +44689,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="382"/>
-      <c r="H16" s="382"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44709,8 +44705,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="382"/>
-      <c r="H17" s="382"/>
+      <c r="G17" s="377"/>
+      <c r="H17" s="377"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44725,8 +44721,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="382"/>
-      <c r="H18" s="382"/>
+      <c r="G18" s="377"/>
+      <c r="H18" s="377"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44740,8 +44736,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="382"/>
-      <c r="H19" s="382"/>
+      <c r="G19" s="377"/>
+      <c r="H19" s="377"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44755,8 +44751,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="382"/>
-      <c r="H20" s="382"/>
+      <c r="G20" s="377"/>
+      <c r="H20" s="377"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44770,8 +44766,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="382"/>
-      <c r="H21" s="382"/>
+      <c r="G21" s="377"/>
+      <c r="H21" s="377"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -44796,9 +44792,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="379"/>
-      <c r="C23" s="380"/>
-      <c r="D23" s="381"/>
+      <c r="B23" s="384"/>
+      <c r="C23" s="385"/>
+      <c r="D23" s="386"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -44810,10 +44806,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="376"/>
-      <c r="B24" s="377"/>
-      <c r="C24" s="377"/>
-      <c r="D24" s="378"/>
+      <c r="A24" s="381"/>
+      <c r="B24" s="382"/>
+      <c r="C24" s="382"/>
+      <c r="D24" s="383"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -44926,9 +44922,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="379"/>
-      <c r="C34" s="380"/>
-      <c r="D34" s="381"/>
+      <c r="B34" s="384"/>
+      <c r="C34" s="385"/>
+      <c r="D34" s="386"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45061,17 +45057,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45092,6 +45088,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -45338,15 +45343,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
   <ds:schemaRefs>
@@ -45359,6 +45355,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73CB8BEA-E38B-414E-AE6B-8CCC019FD87A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45375,12 +45379,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Abril 2026.xlsx
+++ b/data/umr/Resumen UMR Abril 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="26" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E21B53-FD77-490E-A880-70C8D9E435DB}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24216E33-BA7A-49B0-B2DF-8DB1B1667C9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1108,7 +1108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="188">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -1669,6 +1669,9 @@
   </si>
   <si>
     <t>Tren SFC-412 viaje inagural PU-LI y  servicios 405 viaje 72  y 406 viaje 74 retornan en servicio a SA</t>
+  </si>
+  <si>
+    <t>SA-EB</t>
   </si>
 </sst>
 </file>
@@ -3570,7 +3573,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="387">
+  <cellXfs count="388">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -4482,14 +4485,17 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4498,24 +4504,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4531,9 +4519,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4560,6 +4545,27 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4572,9 +4578,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4602,6 +4605,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -5529,37 +5535,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="347" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="347"/>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="347"/>
-      <c r="F1" s="347"/>
-      <c r="G1" s="347"/>
-      <c r="H1" s="347"/>
-      <c r="I1" s="347"/>
-      <c r="J1" s="347"/>
-      <c r="K1" s="347"/>
-      <c r="L1" s="347"/>
-      <c r="M1" s="347"/>
-      <c r="N1" s="347"/>
-      <c r="O1" s="347"/>
-      <c r="P1" s="347"/>
-      <c r="Q1" s="347"/>
-      <c r="R1" s="347"/>
-      <c r="S1" s="347"/>
-      <c r="T1" s="347"/>
-      <c r="U1" s="347"/>
-      <c r="V1" s="347"/>
-      <c r="W1" s="347"/>
-      <c r="X1" s="347"/>
-      <c r="Y1" s="347"/>
-      <c r="Z1" s="347"/>
-      <c r="AA1" s="347"/>
-      <c r="AB1" s="347"/>
-      <c r="AC1" s="347"/>
+      <c r="A1" s="348" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="348"/>
+      <c r="C1" s="348"/>
+      <c r="D1" s="348"/>
+      <c r="E1" s="348"/>
+      <c r="F1" s="348"/>
+      <c r="G1" s="348"/>
+      <c r="H1" s="348"/>
+      <c r="I1" s="348"/>
+      <c r="J1" s="348"/>
+      <c r="K1" s="348"/>
+      <c r="L1" s="348"/>
+      <c r="M1" s="348"/>
+      <c r="N1" s="348"/>
+      <c r="O1" s="348"/>
+      <c r="P1" s="348"/>
+      <c r="Q1" s="348"/>
+      <c r="R1" s="348"/>
+      <c r="S1" s="348"/>
+      <c r="T1" s="348"/>
+      <c r="U1" s="348"/>
+      <c r="V1" s="348"/>
+      <c r="W1" s="348"/>
+      <c r="X1" s="348"/>
+      <c r="Y1" s="348"/>
+      <c r="Z1" s="348"/>
+      <c r="AA1" s="348"/>
+      <c r="AB1" s="348"/>
+      <c r="AC1" s="348"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -9704,37 +9710,37 @@
       <c r="AC46" s="212"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="347" t="s">
+      <c r="A47" s="348" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="347"/>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
-      <c r="G47" s="347"/>
-      <c r="H47" s="347"/>
-      <c r="I47" s="347"/>
-      <c r="J47" s="347"/>
-      <c r="K47" s="347"/>
-      <c r="L47" s="347"/>
-      <c r="M47" s="347"/>
-      <c r="N47" s="347"/>
-      <c r="O47" s="347"/>
-      <c r="P47" s="347"/>
-      <c r="Q47" s="347"/>
-      <c r="R47" s="347"/>
-      <c r="S47" s="347"/>
-      <c r="T47" s="347"/>
-      <c r="U47" s="347"/>
-      <c r="V47" s="347"/>
-      <c r="W47" s="347"/>
-      <c r="X47" s="347"/>
-      <c r="Y47" s="347"/>
-      <c r="Z47" s="347"/>
-      <c r="AA47" s="347"/>
-      <c r="AB47" s="347"/>
-      <c r="AC47" s="347"/>
+      <c r="B47" s="348"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
+      <c r="G47" s="348"/>
+      <c r="H47" s="348"/>
+      <c r="I47" s="348"/>
+      <c r="J47" s="348"/>
+      <c r="K47" s="348"/>
+      <c r="L47" s="348"/>
+      <c r="M47" s="348"/>
+      <c r="N47" s="348"/>
+      <c r="O47" s="348"/>
+      <c r="P47" s="348"/>
+      <c r="Q47" s="348"/>
+      <c r="R47" s="348"/>
+      <c r="S47" s="348"/>
+      <c r="T47" s="348"/>
+      <c r="U47" s="348"/>
+      <c r="V47" s="348"/>
+      <c r="W47" s="348"/>
+      <c r="X47" s="348"/>
+      <c r="Y47" s="348"/>
+      <c r="Z47" s="348"/>
+      <c r="AA47" s="348"/>
+      <c r="AB47" s="348"/>
+      <c r="AC47" s="348"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -15345,14 +15351,14 @@
     </row>
     <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="357" t="s">
+      <c r="B2" s="367" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="357"/>
-      <c r="D2" s="358" t="s">
+      <c r="C2" s="367"/>
+      <c r="D2" s="368" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="358"/>
+      <c r="E2" s="368"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15427,62 +15433,69 @@
       <c r="AD2" s="299">
         <v>10.55</v>
       </c>
+      <c r="AE2" s="232" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF2" s="347">
+        <f>M1-K1</f>
+        <v>3.7100000000000009</v>
+      </c>
     </row>
     <row r="3" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="357" t="s">
+      <c r="B3" s="367" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="357"/>
-      <c r="D3" s="358" t="s">
+      <c r="C3" s="367"/>
+      <c r="D3" s="368" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="358"/>
-      <c r="F3" s="353" t="s">
+      <c r="E3" s="368"/>
+      <c r="F3" s="349" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="353" t="s">
+      <c r="G3" s="349" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="353" t="s">
+      <c r="H3" s="349" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="353" t="s">
+      <c r="I3" s="349" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="353" t="s">
+      <c r="J3" s="349" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="353" t="s">
+      <c r="K3" s="349" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="353" t="s">
+      <c r="L3" s="349" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="353" t="s">
+      <c r="M3" s="349" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="364" t="s">
+      <c r="N3" s="350" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="364" t="s">
+      <c r="O3" s="350" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="363"/>
-      <c r="Q3" s="365" t="s">
+      <c r="P3" s="358"/>
+      <c r="Q3" s="359" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="366"/>
-      <c r="S3" s="367"/>
-      <c r="T3" s="368" t="s">
+      <c r="R3" s="360"/>
+      <c r="S3" s="361"/>
+      <c r="T3" s="362" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="369"/>
-      <c r="V3" s="370"/>
-      <c r="W3" s="361" t="s">
+      <c r="U3" s="363"/>
+      <c r="V3" s="364"/>
+      <c r="W3" s="356" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="361" t="s">
+      <c r="X3" s="356" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15500,17 +15513,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="353"/>
-      <c r="G4" s="354"/>
-      <c r="H4" s="354"/>
-      <c r="I4" s="353"/>
-      <c r="J4" s="353"/>
-      <c r="K4" s="353"/>
-      <c r="L4" s="353"/>
-      <c r="M4" s="353"/>
-      <c r="N4" s="364"/>
-      <c r="O4" s="364"/>
-      <c r="P4" s="363"/>
+      <c r="F4" s="349"/>
+      <c r="G4" s="369"/>
+      <c r="H4" s="369"/>
+      <c r="I4" s="349"/>
+      <c r="J4" s="349"/>
+      <c r="K4" s="349"/>
+      <c r="L4" s="349"/>
+      <c r="M4" s="349"/>
+      <c r="N4" s="350"/>
+      <c r="O4" s="350"/>
+      <c r="P4" s="358"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15529,8 +15542,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="362"/>
-      <c r="X4" s="362"/>
+      <c r="W4" s="357"/>
+      <c r="X4" s="357"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -16540,7 +16553,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="355" t="s">
+      <c r="A20" s="372" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="218">
@@ -16607,7 +16620,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="355"/>
+      <c r="A21" s="372"/>
       <c r="B21" s="218">
         <v>0</v>
       </c>
@@ -16672,7 +16685,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="355"/>
+      <c r="A22" s="372"/>
       <c r="B22" s="218">
         <v>0</v>
       </c>
@@ -16737,7 +16750,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="355"/>
+      <c r="A23" s="372"/>
       <c r="B23" s="218">
         <v>0</v>
       </c>
@@ -16802,7 +16815,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="355"/>
+      <c r="A24" s="372"/>
       <c r="B24" s="218">
         <v>0</v>
       </c>
@@ -17006,7 +17019,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="355" t="s">
+      <c r="A27" s="372" t="s">
         <v>181</v>
       </c>
       <c r="B27" s="218">
@@ -17073,7 +17086,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="355"/>
+      <c r="A28" s="372"/>
       <c r="B28" s="218">
         <v>0</v>
       </c>
@@ -17138,7 +17151,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="355"/>
+      <c r="A29" s="372"/>
       <c r="B29" s="218">
         <v>0</v>
       </c>
@@ -17203,7 +17216,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="355"/>
+      <c r="A30" s="372"/>
       <c r="B30" s="218">
         <v>0</v>
       </c>
@@ -17267,7 +17280,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="355"/>
+      <c r="A31" s="372"/>
       <c r="B31" s="218">
         <v>0</v>
       </c>
@@ -17936,7 +17949,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="356" t="s">
+      <c r="A41" s="373" t="s">
         <v>182</v>
       </c>
       <c r="B41" s="295">
@@ -17991,13 +18004,13 @@
       <c r="R41" s="186"/>
       <c r="S41" s="217"/>
       <c r="T41" s="183">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U41" s="217"/>
       <c r="V41" s="229"/>
       <c r="W41" s="185">
         <f>J41-(T41*($M$2-$K$1)+(U41*($M$2-$M$1)))</f>
-        <v>5147.8100000000004</v>
+        <v>5130.0800000000008</v>
       </c>
       <c r="X41" s="182">
         <f>H41*$M$2</f>
@@ -18005,7 +18018,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="356"/>
+      <c r="A42" s="373"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -18079,7 +18092,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="356"/>
+      <c r="A43" s="373"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -18151,7 +18164,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="356"/>
+      <c r="A44" s="373"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -18223,7 +18236,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="356"/>
+      <c r="A45" s="373"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -18347,7 +18360,7 @@
       </c>
       <c r="O46" s="21">
         <f>(W46/N46)*100</f>
-        <v>96.838205723124531</v>
+        <v>96.701082753286954</v>
       </c>
       <c r="P46" s="192"/>
       <c r="Q46" s="181"/>
@@ -18358,7 +18371,7 @@
       <c r="V46" s="181"/>
       <c r="W46" s="193">
         <f>SUM(W40:W45)</f>
-        <v>12521.180000000002</v>
+        <v>12503.450000000003</v>
       </c>
       <c r="X46" s="193">
         <f>SUM(X40:X45)</f>
@@ -18637,11 +18650,13 @@
       <c r="R50" s="189"/>
       <c r="S50" s="189"/>
       <c r="T50" s="189"/>
-      <c r="U50" s="189"/>
+      <c r="U50" s="189">
+        <v>1</v>
+      </c>
       <c r="V50" s="189"/>
       <c r="W50" s="182">
-        <f>J50</f>
-        <v>960.63</v>
+        <f>J50-U50*AF2</f>
+        <v>956.92</v>
       </c>
       <c r="X50" s="182">
         <f>H50*$M$1</f>
@@ -18831,7 +18846,7 @@
       </c>
       <c r="O53" s="21">
         <f>(W53/N53)*100</f>
-        <v>95.221830716200699</v>
+        <v>95.193412485637722</v>
       </c>
       <c r="P53" s="192"/>
       <c r="Q53" s="181"/>
@@ -18842,7 +18857,7 @@
       <c r="V53" s="181"/>
       <c r="W53" s="193">
         <f>SUM(W47:W52)</f>
-        <v>12431.210000000003</v>
+        <v>12427.500000000004</v>
       </c>
       <c r="X53" s="193">
         <f>SUM(X47:X52)</f>
@@ -18920,7 +18935,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="355" t="s">
+      <c r="A55" s="372" t="s">
         <v>183</v>
       </c>
       <c r="B55" s="295">
@@ -18991,7 +19006,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="355"/>
+      <c r="A56" s="372"/>
       <c r="B56" s="295">
         <v>33</v>
       </c>
@@ -19058,7 +19073,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="355"/>
+      <c r="A57" s="372"/>
       <c r="B57" s="295">
         <v>29</v>
       </c>
@@ -19126,7 +19141,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="355"/>
+      <c r="A58" s="372"/>
       <c r="B58" s="295">
         <v>0</v>
       </c>
@@ -19191,7 +19206,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="355"/>
+      <c r="A59" s="372"/>
       <c r="B59" s="295">
         <v>4</v>
       </c>
@@ -25536,7 +25551,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="356" t="s">
+      <c r="A153" s="373" t="s">
         <v>186</v>
       </c>
       <c r="B153" s="295">
@@ -25607,7 +25622,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="356"/>
+      <c r="A154" s="373"/>
       <c r="B154" s="295">
         <v>33</v>
       </c>
@@ -25676,7 +25691,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="356"/>
+      <c r="A155" s="373"/>
       <c r="B155" s="295">
         <v>29</v>
       </c>
@@ -25743,7 +25758,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="356"/>
+      <c r="A156" s="373"/>
       <c r="B156" s="295">
         <v>0</v>
       </c>
@@ -25810,7 +25825,7 @@
       <c r="Z156" s="124"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="356"/>
+      <c r="A157" s="373"/>
       <c r="B157" s="295">
         <v>4</v>
       </c>
@@ -29905,38 +29920,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="350" t="s">
+      <c r="B223" s="351" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="351"/>
-      <c r="D223" s="351"/>
-      <c r="E223" s="351"/>
-      <c r="F223" s="351"/>
-      <c r="G223" s="352"/>
+      <c r="C223" s="352"/>
+      <c r="D223" s="352"/>
+      <c r="E223" s="352"/>
+      <c r="F223" s="352"/>
+      <c r="G223" s="353"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="350" t="s">
+      <c r="I223" s="351" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="351"/>
-      <c r="K223" s="351"/>
-      <c r="L223" s="351"/>
-      <c r="M223" s="351"/>
-      <c r="N223" s="352"/>
-      <c r="P223" s="371" t="s">
+      <c r="J223" s="352"/>
+      <c r="K223" s="352"/>
+      <c r="L223" s="352"/>
+      <c r="M223" s="352"/>
+      <c r="N223" s="353"/>
+      <c r="P223" s="365" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="371"/>
-      <c r="R223" s="371"/>
-      <c r="S223" s="372"/>
-      <c r="T223" s="368" t="s">
+      <c r="Q223" s="365"/>
+      <c r="R223" s="365"/>
+      <c r="S223" s="366"/>
+      <c r="T223" s="362" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="369"/>
-      <c r="V223" s="370"/>
-      <c r="W223" s="359" t="s">
+      <c r="U223" s="363"/>
+      <c r="V223" s="364"/>
+      <c r="W223" s="354" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="359" t="s">
+      <c r="X223" s="354" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30002,8 +30017,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="360"/>
-      <c r="X224" s="360"/>
+      <c r="W224" s="355"/>
+      <c r="X224" s="355"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30077,7 +30092,7 @@
       </c>
       <c r="T225" s="209">
         <f>SUM(T194,T187,T180,T173,T166,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T201,T208,T215)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T167+T174+T181+T188+T195+T202+T209+T216</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U225" s="209">
         <f>SUM(U194,U187,U180,U173,U166,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U201,U208,U216)</f>
@@ -30089,7 +30104,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>314318.96000000002</v>
+        <v>314297.52</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -30555,10 +30570,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="348" t="s">
+      <c r="B237" s="370" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="349"/>
+      <c r="C237" s="371"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -30734,13 +30749,20 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A153:A157"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:H4"/>
     <mergeCell ref="X223:X224"/>
     <mergeCell ref="W223:W224"/>
     <mergeCell ref="W3:W4"/>
@@ -30751,20 +30773,13 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="P223:S223"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A153:A157"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D194:E199 D187:E192 D180:E185 D173:E178 D166:E171 D159:E164">
     <cfRule type="expression" dxfId="39" priority="134">
@@ -30988,126 +31003,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="373">
+      <c r="D1" s="374">
         <v>46113</v>
       </c>
-      <c r="E1" s="373"/>
-      <c r="F1" s="373">
+      <c r="E1" s="374"/>
+      <c r="F1" s="374">
         <v>46114</v>
       </c>
-      <c r="G1" s="373"/>
-      <c r="H1" s="373">
+      <c r="G1" s="374"/>
+      <c r="H1" s="374">
         <v>46115</v>
       </c>
-      <c r="I1" s="373"/>
-      <c r="J1" s="373">
+      <c r="I1" s="374"/>
+      <c r="J1" s="374">
         <v>46116</v>
       </c>
-      <c r="K1" s="373"/>
-      <c r="L1" s="373">
+      <c r="K1" s="374"/>
+      <c r="L1" s="374">
         <v>46117</v>
       </c>
-      <c r="M1" s="373"/>
-      <c r="N1" s="373">
+      <c r="M1" s="374"/>
+      <c r="N1" s="374">
         <v>46118</v>
       </c>
-      <c r="O1" s="373"/>
-      <c r="P1" s="373">
+      <c r="O1" s="374"/>
+      <c r="P1" s="374">
         <v>46119</v>
       </c>
-      <c r="Q1" s="373"/>
-      <c r="R1" s="373">
+      <c r="Q1" s="374"/>
+      <c r="R1" s="374">
         <v>46120</v>
       </c>
-      <c r="S1" s="373"/>
-      <c r="T1" s="373">
+      <c r="S1" s="374"/>
+      <c r="T1" s="374">
         <v>46121</v>
       </c>
-      <c r="U1" s="373"/>
-      <c r="V1" s="373">
+      <c r="U1" s="374"/>
+      <c r="V1" s="374">
         <v>46122</v>
       </c>
-      <c r="W1" s="373"/>
-      <c r="X1" s="373">
+      <c r="W1" s="374"/>
+      <c r="X1" s="374">
         <v>46123</v>
       </c>
-      <c r="Y1" s="373"/>
-      <c r="Z1" s="373">
+      <c r="Y1" s="374"/>
+      <c r="Z1" s="374">
         <v>46124</v>
       </c>
-      <c r="AA1" s="373"/>
-      <c r="AB1" s="373">
+      <c r="AA1" s="374"/>
+      <c r="AB1" s="374">
         <v>46125</v>
       </c>
-      <c r="AC1" s="373"/>
-      <c r="AD1" s="373">
+      <c r="AC1" s="374"/>
+      <c r="AD1" s="374">
         <v>46126</v>
       </c>
-      <c r="AE1" s="373"/>
-      <c r="AF1" s="373">
+      <c r="AE1" s="374"/>
+      <c r="AF1" s="374">
         <v>46127</v>
       </c>
-      <c r="AG1" s="373"/>
-      <c r="AH1" s="373">
+      <c r="AG1" s="374"/>
+      <c r="AH1" s="374">
         <v>46128</v>
       </c>
-      <c r="AI1" s="373"/>
-      <c r="AJ1" s="373">
+      <c r="AI1" s="374"/>
+      <c r="AJ1" s="374">
         <v>46129</v>
       </c>
-      <c r="AK1" s="373"/>
-      <c r="AL1" s="373">
+      <c r="AK1" s="374"/>
+      <c r="AL1" s="374">
         <v>46130</v>
       </c>
-      <c r="AM1" s="373"/>
-      <c r="AN1" s="373">
+      <c r="AM1" s="374"/>
+      <c r="AN1" s="374">
         <v>46131</v>
       </c>
-      <c r="AO1" s="373"/>
-      <c r="AP1" s="373">
+      <c r="AO1" s="374"/>
+      <c r="AP1" s="374">
         <v>46132</v>
       </c>
-      <c r="AQ1" s="373"/>
-      <c r="AR1" s="373">
+      <c r="AQ1" s="374"/>
+      <c r="AR1" s="374">
         <v>46133</v>
       </c>
-      <c r="AS1" s="373"/>
-      <c r="AT1" s="373">
+      <c r="AS1" s="374"/>
+      <c r="AT1" s="374">
         <v>46134</v>
       </c>
-      <c r="AU1" s="373"/>
-      <c r="AV1" s="373">
+      <c r="AU1" s="374"/>
+      <c r="AV1" s="374">
         <v>46135</v>
       </c>
-      <c r="AW1" s="373"/>
-      <c r="AX1" s="373">
+      <c r="AW1" s="374"/>
+      <c r="AX1" s="374">
         <v>46136</v>
       </c>
-      <c r="AY1" s="373"/>
-      <c r="AZ1" s="373">
+      <c r="AY1" s="374"/>
+      <c r="AZ1" s="374">
         <v>46137</v>
       </c>
-      <c r="BA1" s="373"/>
-      <c r="BB1" s="373">
+      <c r="BA1" s="374"/>
+      <c r="BB1" s="374">
         <v>46138</v>
       </c>
-      <c r="BC1" s="373"/>
-      <c r="BD1" s="373">
+      <c r="BC1" s="374"/>
+      <c r="BD1" s="374">
         <v>46139</v>
       </c>
-      <c r="BE1" s="373"/>
-      <c r="BF1" s="373">
+      <c r="BE1" s="374"/>
+      <c r="BF1" s="374">
         <v>46140</v>
       </c>
-      <c r="BG1" s="373"/>
-      <c r="BH1" s="373">
+      <c r="BG1" s="374"/>
+      <c r="BH1" s="374">
         <v>46141</v>
       </c>
-      <c r="BI1" s="373"/>
-      <c r="BJ1" s="373">
+      <c r="BI1" s="374"/>
+      <c r="BJ1" s="374">
         <v>46142</v>
       </c>
-      <c r="BK1" s="373"/>
+      <c r="BK1" s="374"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -36873,10 +36888,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="374" t="s">
+      <c r="A37" s="375" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="374"/>
+      <c r="B37" s="375"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="13">SUM(D31:D36)</f>
@@ -39346,6 +39361,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -39362,21 +39392,6 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -41254,7 +41269,7 @@
       </c>
       <c r="H20" s="83">
         <f>'KM-Servicio'!T41</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="83">
         <f>'KM-Servicio'!T48</f>
@@ -41996,7 +42011,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>314318.96000000002</v>
+        <v>314301.23</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42020,7 +42035,7 @@
       </c>
       <c r="H29" s="91">
         <f>(H12*$B$12+H13*$B$13+H14*$B$14+H15*$B$15+H17*$B$17+H20*$B$20+H16*$B$16+H19*$B$19+H21*$B$21+H22*$B$22+H23*B23+H25*B25)</f>
-        <v>12521.180000000002</v>
+        <v>12503.450000000003</v>
       </c>
       <c r="I29" s="91">
         <f>(I12*$B$12+I13*$B$13+I14*$B$14+I15*$B$15+I17*$B$17+I20*$B$20+I16*$B$16+I19*$B$19+I21*$B$21+I22*$B$22+I24*B24)</f>
@@ -42254,7 +42269,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32689171.840000004</v>
+        <v>32687327.920000006</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -42278,7 +42293,7 @@
       </c>
       <c r="H31" s="91">
         <f t="shared" si="12"/>
-        <v>1302202.7200000002</v>
+        <v>1300358.8000000003</v>
       </c>
       <c r="I31" s="91">
         <f t="shared" si="12"/>
@@ -42383,7 +42398,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>628637.92000000004</v>
+        <v>628602.46</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -42407,7 +42422,7 @@
       </c>
       <c r="H32" s="91">
         <f t="shared" si="15"/>
-        <v>25042.360000000004</v>
+        <v>25006.900000000005</v>
       </c>
       <c r="I32" s="91">
         <f t="shared" si="15"/>
@@ -42641,7 +42656,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24925493.528000005</v>
+        <v>24924087.539000005</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -42665,7 +42680,7 @@
       </c>
       <c r="H34" s="91">
         <f t="shared" si="21"/>
-        <v>992929.57400000014</v>
+        <v>991523.5850000002</v>
       </c>
       <c r="I34" s="91">
         <f t="shared" si="21"/>
@@ -43075,19 +43090,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="375" t="s">
+      <c r="A2" s="376" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="376"/>
-      <c r="C2" s="376"/>
-      <c r="D2" s="376"/>
-      <c r="E2" s="376"/>
-      <c r="F2" s="376"/>
-      <c r="G2" s="376"/>
-      <c r="H2" s="376"/>
-      <c r="I2" s="376"/>
-      <c r="J2" s="376"/>
-      <c r="K2" s="376"/>
+      <c r="B2" s="377"/>
+      <c r="C2" s="377"/>
+      <c r="D2" s="377"/>
+      <c r="E2" s="377"/>
+      <c r="F2" s="377"/>
+      <c r="G2" s="377"/>
+      <c r="H2" s="377"/>
+      <c r="I2" s="377"/>
+      <c r="J2" s="377"/>
+      <c r="K2" s="377"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -43348,15 +43363,15 @@
       </c>
       <c r="D9" s="342">
         <f>'KM-Servicio'!W46</f>
-        <v>12521.180000000002</v>
+        <v>12503.450000000003</v>
       </c>
       <c r="E9" s="312">
         <f t="shared" si="1"/>
-        <v>52374.61</v>
+        <v>52356.880000000005</v>
       </c>
       <c r="F9" s="313">
         <f>'KM-Servicio'!O46</f>
-        <v>96.838205723124531</v>
+        <v>96.701082753286954</v>
       </c>
       <c r="G9" s="314">
         <f>SUM('KM-Servicio'!B46:C46)</f>
@@ -43368,7 +43383,7 @@
       </c>
       <c r="I9" s="312">
         <f>'Oferta Diaria'!H34</f>
-        <v>992929.57400000014</v>
+        <v>991523.5850000002</v>
       </c>
       <c r="J9" s="161" t="s">
         <v>137</v>
@@ -43390,15 +43405,15 @@
       </c>
       <c r="D10" s="342">
         <f>'KM-Servicio'!W53</f>
-        <v>12431.210000000003</v>
+        <v>12427.500000000004</v>
       </c>
       <c r="E10" s="312">
         <f t="shared" si="1"/>
-        <v>64805.820000000007</v>
+        <v>64784.380000000005</v>
       </c>
       <c r="F10" s="313">
         <f>'KM-Servicio'!O53</f>
-        <v>95.221830716200699</v>
+        <v>95.193412485637722</v>
       </c>
       <c r="G10" s="314">
         <f>SUM('KM-Servicio'!B53:C53)</f>
@@ -43436,7 +43451,7 @@
       </c>
       <c r="E11" s="312">
         <f t="shared" si="1"/>
-        <v>76914.930000000008</v>
+        <v>76893.490000000005</v>
       </c>
       <c r="F11" s="313">
         <f>'KM-Servicio'!O60</f>
@@ -43478,7 +43493,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>89486.91</v>
+        <v>89465.47</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -43520,7 +43535,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>102165.27</v>
+        <v>102143.83</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -43562,7 +43577,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>108634.77</v>
+        <v>108613.33</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -43604,7 +43619,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113551.59000000001</v>
+        <v>113530.15000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -43646,7 +43661,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>126004.24000000002</v>
+        <v>125982.80000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O95</f>
@@ -43688,7 +43703,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138578.61000000002</v>
+        <v>138557.17000000001</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O102</f>
@@ -43730,7 +43745,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151131.54</v>
+        <v>151110.1</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
@@ -43772,7 +43787,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>163776.83000000002</v>
+        <v>163755.39000000001</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -43813,7 +43828,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>176312.03000000003</v>
+        <v>176290.59000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -43855,7 +43870,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>182781.53000000003</v>
+        <v>182760.09000000003</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -43897,7 +43912,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187784.61000000002</v>
+        <v>187763.17</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -43939,7 +43954,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>200374.32</v>
+        <v>200352.88</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O144</f>
@@ -43981,7 +43996,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>212809.24000000002</v>
+        <v>212787.80000000002</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O151</f>
@@ -44023,7 +44038,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>225604.29</v>
+        <v>225582.85</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -44065,7 +44080,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>238107.74000000002</v>
+        <v>238086.30000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44107,7 +44122,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>250512.23</v>
+        <v>250490.79</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44149,7 +44164,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>256981.73</v>
+        <v>256960.29</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44191,7 +44206,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>261898.55000000002</v>
+        <v>261877.11000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44233,7 +44248,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>274881.21000000002</v>
+        <v>274859.77</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44275,7 +44290,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>289294.33</v>
+        <v>289272.89</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44317,7 +44332,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>301797.78000000003</v>
+        <v>301776.34000000003</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44359,11 +44374,11 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>314318.96000000002</v>
+        <v>314297.52</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
-        <v>96.838205723124531</v>
+        <v>96.701082753286954</v>
       </c>
       <c r="G33" s="167">
         <f>'KM-Servicio'!B214+'KM-Servicio'!C214</f>
@@ -44431,15 +44446,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>314318.96000000002</v>
+        <v>314297.52</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4702972.6100000003</v>
+        <v>4702440.32</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.23006712375846</v>
+        <v>97.219978318083832</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44451,7 +44466,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24925493.528000005</v>
+        <v>24924087.539000005</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -44689,8 +44704,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="377"/>
-      <c r="H16" s="377"/>
+      <c r="G16" s="387"/>
+      <c r="H16" s="387"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44705,8 +44720,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="377"/>
-      <c r="H17" s="377"/>
+      <c r="G17" s="387"/>
+      <c r="H17" s="387"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44721,8 +44736,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
+      <c r="G18" s="387"/>
+      <c r="H18" s="387"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44736,8 +44751,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="377"/>
-      <c r="H19" s="377"/>
+      <c r="G19" s="387"/>
+      <c r="H19" s="387"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44751,8 +44766,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="377"/>
-      <c r="H20" s="377"/>
+      <c r="G20" s="387"/>
+      <c r="H20" s="387"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44766,8 +44781,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="377"/>
-      <c r="H21" s="377"/>
+      <c r="G21" s="387"/>
+      <c r="H21" s="387"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -45057,17 +45072,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45088,15 +45103,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -45343,6 +45349,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
   <ds:schemaRefs>
@@ -45355,14 +45370,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73CB8BEA-E38B-414E-AE6B-8CCC019FD87A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45379,4 +45386,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Abril 2026.xlsx
+++ b/data/umr/Resumen UMR Abril 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="35" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24216E33-BA7A-49B0-B2DF-8DB1B1667C9E}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB082D29-6650-4481-A85D-4F336B809E1A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -1108,7 +1108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="189">
   <si>
     <t>Control Contador Kilometraje de Trenes</t>
   </si>
@@ -1672,6 +1672,9 @@
   </si>
   <si>
     <t>SA-EB</t>
+  </si>
+  <si>
+    <t>LI-SA</t>
   </si>
 </sst>
 </file>
@@ -3573,7 +3576,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="388">
+  <cellXfs count="389">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
@@ -4488,14 +4491,17 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4504,6 +4510,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4519,6 +4543,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4545,27 +4572,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4578,6 +4584,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4605,9 +4614,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -5535,37 +5541,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="348" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="348"/>
-      <c r="C1" s="348"/>
-      <c r="D1" s="348"/>
-      <c r="E1" s="348"/>
-      <c r="F1" s="348"/>
-      <c r="G1" s="348"/>
-      <c r="H1" s="348"/>
-      <c r="I1" s="348"/>
-      <c r="J1" s="348"/>
-      <c r="K1" s="348"/>
-      <c r="L1" s="348"/>
-      <c r="M1" s="348"/>
-      <c r="N1" s="348"/>
-      <c r="O1" s="348"/>
-      <c r="P1" s="348"/>
-      <c r="Q1" s="348"/>
-      <c r="R1" s="348"/>
-      <c r="S1" s="348"/>
-      <c r="T1" s="348"/>
-      <c r="U1" s="348"/>
-      <c r="V1" s="348"/>
-      <c r="W1" s="348"/>
-      <c r="X1" s="348"/>
-      <c r="Y1" s="348"/>
-      <c r="Z1" s="348"/>
-      <c r="AA1" s="348"/>
-      <c r="AB1" s="348"/>
-      <c r="AC1" s="348"/>
+      <c r="A1" s="349" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="349"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
+      <c r="I1" s="349"/>
+      <c r="J1" s="349"/>
+      <c r="K1" s="349"/>
+      <c r="L1" s="349"/>
+      <c r="M1" s="349"/>
+      <c r="N1" s="349"/>
+      <c r="O1" s="349"/>
+      <c r="P1" s="349"/>
+      <c r="Q1" s="349"/>
+      <c r="R1" s="349"/>
+      <c r="S1" s="349"/>
+      <c r="T1" s="349"/>
+      <c r="U1" s="349"/>
+      <c r="V1" s="349"/>
+      <c r="W1" s="349"/>
+      <c r="X1" s="349"/>
+      <c r="Y1" s="349"/>
+      <c r="Z1" s="349"/>
+      <c r="AA1" s="349"/>
+      <c r="AB1" s="349"/>
+      <c r="AC1" s="349"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -9710,37 +9716,37 @@
       <c r="AC46" s="212"/>
     </row>
     <row r="47" spans="1:31" ht="18" x14ac:dyDescent="0.25">
-      <c r="A47" s="348" t="s">
+      <c r="A47" s="349" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="348"/>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
-      <c r="G47" s="348"/>
-      <c r="H47" s="348"/>
-      <c r="I47" s="348"/>
-      <c r="J47" s="348"/>
-      <c r="K47" s="348"/>
-      <c r="L47" s="348"/>
-      <c r="M47" s="348"/>
-      <c r="N47" s="348"/>
-      <c r="O47" s="348"/>
-      <c r="P47" s="348"/>
-      <c r="Q47" s="348"/>
-      <c r="R47" s="348"/>
-      <c r="S47" s="348"/>
-      <c r="T47" s="348"/>
-      <c r="U47" s="348"/>
-      <c r="V47" s="348"/>
-      <c r="W47" s="348"/>
-      <c r="X47" s="348"/>
-      <c r="Y47" s="348"/>
-      <c r="Z47" s="348"/>
-      <c r="AA47" s="348"/>
-      <c r="AB47" s="348"/>
-      <c r="AC47" s="348"/>
+      <c r="B47" s="349"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
+      <c r="G47" s="349"/>
+      <c r="H47" s="349"/>
+      <c r="I47" s="349"/>
+      <c r="J47" s="349"/>
+      <c r="K47" s="349"/>
+      <c r="L47" s="349"/>
+      <c r="M47" s="349"/>
+      <c r="N47" s="349"/>
+      <c r="O47" s="349"/>
+      <c r="P47" s="349"/>
+      <c r="Q47" s="349"/>
+      <c r="R47" s="349"/>
+      <c r="S47" s="349"/>
+      <c r="T47" s="349"/>
+      <c r="U47" s="349"/>
+      <c r="V47" s="349"/>
+      <c r="W47" s="349"/>
+      <c r="X47" s="349"/>
+      <c r="Y47" s="349"/>
+      <c r="Z47" s="349"/>
+      <c r="AA47" s="349"/>
+      <c r="AB47" s="349"/>
+      <c r="AC47" s="349"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
@@ -15265,7 +15271,7 @@
     <col min="22" max="22" width="7.85546875" style="124" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="17"/>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -15348,17 +15354,24 @@
       <c r="AF1" s="307">
         <v>21.43</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AG1" s="232" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH1" s="348">
+        <f>M2-M1</f>
+        <v>14.020000000000003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="367" t="s">
+      <c r="B2" s="359" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="367"/>
-      <c r="D2" s="368" t="s">
+      <c r="C2" s="359"/>
+      <c r="D2" s="360" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="368"/>
+      <c r="E2" s="360"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15441,65 +15454,65 @@
         <v>3.7100000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="367" t="s">
+      <c r="B3" s="359" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="367"/>
-      <c r="D3" s="368" t="s">
+      <c r="C3" s="359"/>
+      <c r="D3" s="360" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="368"/>
-      <c r="F3" s="349" t="s">
+      <c r="E3" s="360"/>
+      <c r="F3" s="355" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="349" t="s">
+      <c r="G3" s="355" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="349" t="s">
+      <c r="H3" s="355" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="349" t="s">
+      <c r="I3" s="355" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="349" t="s">
+      <c r="J3" s="355" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="355" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="349" t="s">
+      <c r="L3" s="355" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="349" t="s">
+      <c r="M3" s="355" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="350" t="s">
+      <c r="N3" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="350" t="s">
+      <c r="O3" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="358"/>
-      <c r="Q3" s="359" t="s">
+      <c r="P3" s="365"/>
+      <c r="Q3" s="367" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="360"/>
-      <c r="S3" s="361"/>
-      <c r="T3" s="362" t="s">
+      <c r="R3" s="368"/>
+      <c r="S3" s="369"/>
+      <c r="T3" s="370" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="363"/>
-      <c r="V3" s="364"/>
-      <c r="W3" s="356" t="s">
+      <c r="U3" s="371"/>
+      <c r="V3" s="372"/>
+      <c r="W3" s="363" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="356" t="s">
+      <c r="X3" s="363" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="41" t="s">
         <v>50</v>
@@ -15513,17 +15526,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="349"/>
-      <c r="G4" s="369"/>
-      <c r="H4" s="369"/>
-      <c r="I4" s="349"/>
-      <c r="J4" s="349"/>
-      <c r="K4" s="349"/>
-      <c r="L4" s="349"/>
-      <c r="M4" s="349"/>
-      <c r="N4" s="350"/>
-      <c r="O4" s="350"/>
-      <c r="P4" s="358"/>
+      <c r="F4" s="355"/>
+      <c r="G4" s="356"/>
+      <c r="H4" s="356"/>
+      <c r="I4" s="355"/>
+      <c r="J4" s="355"/>
+      <c r="K4" s="355"/>
+      <c r="L4" s="355"/>
+      <c r="M4" s="355"/>
+      <c r="N4" s="366"/>
+      <c r="O4" s="366"/>
+      <c r="P4" s="365"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15542,10 +15555,10 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="357"/>
-      <c r="X4" s="357"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="W4" s="364"/>
+      <c r="X4" s="364"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>46113</v>
       </c>
@@ -15614,7 +15627,7 @@
         <v>4830.5600000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="202"/>
       <c r="B6" s="295">
         <v>44</v>
@@ -15681,7 +15694,7 @@
         <v>4830.5600000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="202"/>
       <c r="B7" s="295">
         <v>33</v>
@@ -15748,7 +15761,7 @@
         <v>1135.29</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="202"/>
       <c r="B8" s="295">
         <v>28</v>
@@ -15813,7 +15826,7 @@
         <v>1047.96</v>
       </c>
     </row>
-    <row r="9" spans="1:32" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="202"/>
       <c r="B9" s="295">
         <v>0</v>
@@ -15878,7 +15891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="202"/>
       <c r="B10" s="295">
         <v>4</v>
@@ -15943,7 +15956,7 @@
         <v>101.6</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="119">
         <f>SUM(B5:B10)</f>
@@ -16015,7 +16028,7 @@
       </c>
       <c r="AA11" s="172"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <f>A5+1</f>
         <v>46114</v>
@@ -16084,7 +16097,7 @@
       </c>
       <c r="Z12" s="124"/>
     </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="202"/>
       <c r="B13" s="295">
         <v>44</v>
@@ -16152,7 +16165,7 @@
       </c>
       <c r="Z13" s="124"/>
     </row>
-    <row r="14" spans="1:32" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="202"/>
       <c r="B14" s="295">
         <v>33</v>
@@ -16218,7 +16231,7 @@
       </c>
       <c r="Z14" s="124"/>
     </row>
-    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="202"/>
       <c r="B15" s="295">
         <v>28</v>
@@ -16283,7 +16296,7 @@
         <v>1047.96</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="202"/>
       <c r="B16" s="295">
         <v>0</v>
@@ -16553,7 +16566,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="372" t="s">
+      <c r="A20" s="357" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="218">
@@ -16620,7 +16633,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="372"/>
+      <c r="A21" s="357"/>
       <c r="B21" s="218">
         <v>0</v>
       </c>
@@ -16685,7 +16698,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="372"/>
+      <c r="A22" s="357"/>
       <c r="B22" s="218">
         <v>0</v>
       </c>
@@ -16750,7 +16763,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="372"/>
+      <c r="A23" s="357"/>
       <c r="B23" s="218">
         <v>0</v>
       </c>
@@ -16815,7 +16828,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="372"/>
+      <c r="A24" s="357"/>
       <c r="B24" s="218">
         <v>0</v>
       </c>
@@ -17019,7 +17032,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="372" t="s">
+      <c r="A27" s="357" t="s">
         <v>181</v>
       </c>
       <c r="B27" s="218">
@@ -17086,7 +17099,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="372"/>
+      <c r="A28" s="357"/>
       <c r="B28" s="218">
         <v>0</v>
       </c>
@@ -17151,7 +17164,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="372"/>
+      <c r="A29" s="357"/>
       <c r="B29" s="218">
         <v>0</v>
       </c>
@@ -17216,7 +17229,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="372"/>
+      <c r="A30" s="357"/>
       <c r="B30" s="218">
         <v>0</v>
       </c>
@@ -17280,7 +17293,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="372"/>
+      <c r="A31" s="357"/>
       <c r="B31" s="218">
         <v>0</v>
       </c>
@@ -17949,7 +17962,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="373" t="s">
+      <c r="A41" s="358" t="s">
         <v>182</v>
       </c>
       <c r="B41" s="295">
@@ -18018,7 +18031,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="373"/>
+      <c r="A42" s="358"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -18092,7 +18105,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="373"/>
+      <c r="A43" s="358"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -18164,7 +18177,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="373"/>
+      <c r="A44" s="358"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -18236,7 +18249,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="373"/>
+      <c r="A45" s="358"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -18655,8 +18668,8 @@
       </c>
       <c r="V50" s="189"/>
       <c r="W50" s="182">
-        <f>J50-U50*AF2</f>
-        <v>956.92</v>
+        <f>J50-U50*AH1</f>
+        <v>946.61</v>
       </c>
       <c r="X50" s="182">
         <f>H50*$M$1</f>
@@ -18846,7 +18859,7 @@
       </c>
       <c r="O53" s="21">
         <f>(W53/N53)*100</f>
-        <v>95.193412485637722</v>
+        <v>95.114438912294176</v>
       </c>
       <c r="P53" s="192"/>
       <c r="Q53" s="181"/>
@@ -18857,7 +18870,7 @@
       <c r="V53" s="181"/>
       <c r="W53" s="193">
         <f>SUM(W47:W52)</f>
-        <v>12427.500000000004</v>
+        <v>12417.190000000004</v>
       </c>
       <c r="X53" s="193">
         <f>SUM(X47:X52)</f>
@@ -18935,7 +18948,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="372" t="s">
+      <c r="A55" s="357" t="s">
         <v>183</v>
       </c>
       <c r="B55" s="295">
@@ -19006,7 +19019,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="372"/>
+      <c r="A56" s="357"/>
       <c r="B56" s="295">
         <v>33</v>
       </c>
@@ -19073,7 +19086,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="372"/>
+      <c r="A57" s="357"/>
       <c r="B57" s="295">
         <v>29</v>
       </c>
@@ -19141,7 +19154,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="372"/>
+      <c r="A58" s="357"/>
       <c r="B58" s="295">
         <v>0</v>
       </c>
@@ -19206,7 +19219,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="372"/>
+      <c r="A59" s="357"/>
       <c r="B59" s="295">
         <v>4</v>
       </c>
@@ -25551,7 +25564,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="373" t="s">
+      <c r="A153" s="358" t="s">
         <v>186</v>
       </c>
       <c r="B153" s="295">
@@ -25622,7 +25635,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="373"/>
+      <c r="A154" s="358"/>
       <c r="B154" s="295">
         <v>33</v>
       </c>
@@ -25691,7 +25704,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="373"/>
+      <c r="A155" s="358"/>
       <c r="B155" s="295">
         <v>29</v>
       </c>
@@ -25758,7 +25771,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="373"/>
+      <c r="A156" s="358"/>
       <c r="B156" s="295">
         <v>0</v>
       </c>
@@ -25825,7 +25838,7 @@
       <c r="Z156" s="124"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="373"/>
+      <c r="A157" s="358"/>
       <c r="B157" s="295">
         <v>4</v>
       </c>
@@ -29920,38 +29933,38 @@
     <row r="222" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="223" spans="1:28" s="124" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223"/>
-      <c r="B223" s="351" t="s">
+      <c r="B223" s="352" t="s">
         <v>56</v>
       </c>
-      <c r="C223" s="352"/>
-      <c r="D223" s="352"/>
-      <c r="E223" s="352"/>
-      <c r="F223" s="352"/>
-      <c r="G223" s="353"/>
+      <c r="C223" s="353"/>
+      <c r="D223" s="353"/>
+      <c r="E223" s="353"/>
+      <c r="F223" s="353"/>
+      <c r="G223" s="354"/>
       <c r="H223" s="290"/>
-      <c r="I223" s="351" t="s">
+      <c r="I223" s="352" t="s">
         <v>57</v>
       </c>
-      <c r="J223" s="352"/>
-      <c r="K223" s="352"/>
-      <c r="L223" s="352"/>
-      <c r="M223" s="352"/>
-      <c r="N223" s="353"/>
-      <c r="P223" s="365" t="s">
+      <c r="J223" s="353"/>
+      <c r="K223" s="353"/>
+      <c r="L223" s="353"/>
+      <c r="M223" s="353"/>
+      <c r="N223" s="354"/>
+      <c r="P223" s="373" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="365"/>
-      <c r="R223" s="365"/>
-      <c r="S223" s="366"/>
-      <c r="T223" s="362" t="s">
+      <c r="Q223" s="373"/>
+      <c r="R223" s="373"/>
+      <c r="S223" s="374"/>
+      <c r="T223" s="370" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="363"/>
-      <c r="V223" s="364"/>
-      <c r="W223" s="354" t="s">
+      <c r="U223" s="371"/>
+      <c r="V223" s="372"/>
+      <c r="W223" s="361" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="354" t="s">
+      <c r="X223" s="361" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30017,8 +30030,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="355"/>
-      <c r="X224" s="355"/>
+      <c r="W224" s="362"/>
+      <c r="X224" s="362"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30104,7 +30117,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>314297.52</v>
+        <v>314287.21000000002</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -30570,10 +30583,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="370" t="s">
+      <c r="B237" s="350" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="371"/>
+      <c r="C237" s="351"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -30749,20 +30762,13 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A153:A157"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="X223:X224"/>
     <mergeCell ref="W223:W224"/>
     <mergeCell ref="W3:W4"/>
@@ -30773,13 +30779,20 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="P223:S223"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A153:A157"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D194:E199 D187:E192 D180:E185 D173:E178 D166:E171 D159:E164">
     <cfRule type="expression" dxfId="39" priority="134">
@@ -31003,126 +31016,126 @@
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.25">
       <c r="C1" s="8"/>
-      <c r="D1" s="374">
+      <c r="D1" s="375">
         <v>46113</v>
       </c>
-      <c r="E1" s="374"/>
-      <c r="F1" s="374">
+      <c r="E1" s="375"/>
+      <c r="F1" s="375">
         <v>46114</v>
       </c>
-      <c r="G1" s="374"/>
-      <c r="H1" s="374">
+      <c r="G1" s="375"/>
+      <c r="H1" s="375">
         <v>46115</v>
       </c>
-      <c r="I1" s="374"/>
-      <c r="J1" s="374">
+      <c r="I1" s="375"/>
+      <c r="J1" s="375">
         <v>46116</v>
       </c>
-      <c r="K1" s="374"/>
-      <c r="L1" s="374">
+      <c r="K1" s="375"/>
+      <c r="L1" s="375">
         <v>46117</v>
       </c>
-      <c r="M1" s="374"/>
-      <c r="N1" s="374">
+      <c r="M1" s="375"/>
+      <c r="N1" s="375">
         <v>46118</v>
       </c>
-      <c r="O1" s="374"/>
-      <c r="P1" s="374">
+      <c r="O1" s="375"/>
+      <c r="P1" s="375">
         <v>46119</v>
       </c>
-      <c r="Q1" s="374"/>
-      <c r="R1" s="374">
+      <c r="Q1" s="375"/>
+      <c r="R1" s="375">
         <v>46120</v>
       </c>
-      <c r="S1" s="374"/>
-      <c r="T1" s="374">
+      <c r="S1" s="375"/>
+      <c r="T1" s="375">
         <v>46121</v>
       </c>
-      <c r="U1" s="374"/>
-      <c r="V1" s="374">
+      <c r="U1" s="375"/>
+      <c r="V1" s="375">
         <v>46122</v>
       </c>
-      <c r="W1" s="374"/>
-      <c r="X1" s="374">
+      <c r="W1" s="375"/>
+      <c r="X1" s="375">
         <v>46123</v>
       </c>
-      <c r="Y1" s="374"/>
-      <c r="Z1" s="374">
+      <c r="Y1" s="375"/>
+      <c r="Z1" s="375">
         <v>46124</v>
       </c>
-      <c r="AA1" s="374"/>
-      <c r="AB1" s="374">
+      <c r="AA1" s="375"/>
+      <c r="AB1" s="375">
         <v>46125</v>
       </c>
-      <c r="AC1" s="374"/>
-      <c r="AD1" s="374">
+      <c r="AC1" s="375"/>
+      <c r="AD1" s="375">
         <v>46126</v>
       </c>
-      <c r="AE1" s="374"/>
-      <c r="AF1" s="374">
+      <c r="AE1" s="375"/>
+      <c r="AF1" s="375">
         <v>46127</v>
       </c>
-      <c r="AG1" s="374"/>
-      <c r="AH1" s="374">
+      <c r="AG1" s="375"/>
+      <c r="AH1" s="375">
         <v>46128</v>
       </c>
-      <c r="AI1" s="374"/>
-      <c r="AJ1" s="374">
+      <c r="AI1" s="375"/>
+      <c r="AJ1" s="375">
         <v>46129</v>
       </c>
-      <c r="AK1" s="374"/>
-      <c r="AL1" s="374">
+      <c r="AK1" s="375"/>
+      <c r="AL1" s="375">
         <v>46130</v>
       </c>
-      <c r="AM1" s="374"/>
-      <c r="AN1" s="374">
+      <c r="AM1" s="375"/>
+      <c r="AN1" s="375">
         <v>46131</v>
       </c>
-      <c r="AO1" s="374"/>
-      <c r="AP1" s="374">
+      <c r="AO1" s="375"/>
+      <c r="AP1" s="375">
         <v>46132</v>
       </c>
-      <c r="AQ1" s="374"/>
-      <c r="AR1" s="374">
+      <c r="AQ1" s="375"/>
+      <c r="AR1" s="375">
         <v>46133</v>
       </c>
-      <c r="AS1" s="374"/>
-      <c r="AT1" s="374">
+      <c r="AS1" s="375"/>
+      <c r="AT1" s="375">
         <v>46134</v>
       </c>
-      <c r="AU1" s="374"/>
-      <c r="AV1" s="374">
+      <c r="AU1" s="375"/>
+      <c r="AV1" s="375">
         <v>46135</v>
       </c>
-      <c r="AW1" s="374"/>
-      <c r="AX1" s="374">
+      <c r="AW1" s="375"/>
+      <c r="AX1" s="375">
         <v>46136</v>
       </c>
-      <c r="AY1" s="374"/>
-      <c r="AZ1" s="374">
+      <c r="AY1" s="375"/>
+      <c r="AZ1" s="375">
         <v>46137</v>
       </c>
-      <c r="BA1" s="374"/>
-      <c r="BB1" s="374">
+      <c r="BA1" s="375"/>
+      <c r="BB1" s="375">
         <v>46138</v>
       </c>
-      <c r="BC1" s="374"/>
-      <c r="BD1" s="374">
+      <c r="BC1" s="375"/>
+      <c r="BD1" s="375">
         <v>46139</v>
       </c>
-      <c r="BE1" s="374"/>
-      <c r="BF1" s="374">
+      <c r="BE1" s="375"/>
+      <c r="BF1" s="375">
         <v>46140</v>
       </c>
-      <c r="BG1" s="374"/>
-      <c r="BH1" s="374">
+      <c r="BG1" s="375"/>
+      <c r="BH1" s="375">
         <v>46141</v>
       </c>
-      <c r="BI1" s="374"/>
-      <c r="BJ1" s="374">
+      <c r="BI1" s="375"/>
+      <c r="BJ1" s="375">
         <v>46142</v>
       </c>
-      <c r="BK1" s="374"/>
+      <c r="BK1" s="375"/>
     </row>
     <row r="2" spans="1:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
@@ -36888,10 +36901,10 @@
       </c>
     </row>
     <row r="37" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A37" s="375" t="s">
+      <c r="A37" s="376" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="375"/>
+      <c r="B37" s="376"/>
       <c r="C37" s="8"/>
       <c r="D37" s="149">
         <f t="shared" ref="D37:AI37" si="13">SUM(D31:D36)</f>
@@ -39361,21 +39374,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -39392,6 +39390,21 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43090,19 +43103,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="376" t="s">
+      <c r="A2" s="377" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
-      <c r="K2" s="377"/>
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="378"/>
+      <c r="I2" s="378"/>
+      <c r="J2" s="378"/>
+      <c r="K2" s="378"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="158" t="s">
@@ -43405,15 +43418,15 @@
       </c>
       <c r="D10" s="342">
         <f>'KM-Servicio'!W53</f>
-        <v>12427.500000000004</v>
+        <v>12417.190000000004</v>
       </c>
       <c r="E10" s="312">
         <f t="shared" si="1"/>
-        <v>64784.380000000005</v>
+        <v>64774.070000000007</v>
       </c>
       <c r="F10" s="313">
         <f>'KM-Servicio'!O53</f>
-        <v>95.193412485637722</v>
+        <v>95.114438912294176</v>
       </c>
       <c r="G10" s="314">
         <f>SUM('KM-Servicio'!B53:C53)</f>
@@ -43451,7 +43464,7 @@
       </c>
       <c r="E11" s="312">
         <f t="shared" si="1"/>
-        <v>76893.490000000005</v>
+        <v>76883.180000000008</v>
       </c>
       <c r="F11" s="313">
         <f>'KM-Servicio'!O60</f>
@@ -43493,7 +43506,7 @@
       </c>
       <c r="E12" s="12">
         <f t="shared" si="1"/>
-        <v>89465.47</v>
+        <v>89455.16</v>
       </c>
       <c r="F12" s="166">
         <f>'KM-Servicio'!O67</f>
@@ -43535,7 +43548,7 @@
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>102143.83</v>
+        <v>102133.52</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
@@ -43577,7 +43590,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>108613.33</v>
+        <v>108603.02</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -43619,7 +43632,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113530.15000000001</v>
+        <v>113519.84000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -43661,7 +43674,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>125982.80000000002</v>
+        <v>125972.49000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O95</f>
@@ -43703,7 +43716,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138557.17000000001</v>
+        <v>138546.86000000002</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O102</f>
@@ -43745,7 +43758,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151110.1</v>
+        <v>151099.79</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
@@ -43787,7 +43800,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>163755.39000000001</v>
+        <v>163745.08000000002</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -43828,7 +43841,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>176290.59000000003</v>
+        <v>176280.28000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -43870,7 +43883,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>182760.09000000003</v>
+        <v>182749.78000000003</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -43912,7 +43925,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187763.17</v>
+        <v>187752.86000000002</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -43954,7 +43967,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>200352.88</v>
+        <v>200342.57</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O144</f>
@@ -43996,7 +44009,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>212787.80000000002</v>
+        <v>212777.49000000002</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O151</f>
@@ -44038,7 +44051,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>225582.85</v>
+        <v>225572.54</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -44080,7 +44093,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>238086.30000000002</v>
+        <v>238075.99000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44122,7 +44135,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>250490.79</v>
+        <v>250480.48</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44164,7 +44177,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>256960.29</v>
+        <v>256949.98</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44206,7 +44219,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>261877.11000000002</v>
+        <v>261866.80000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44248,7 +44261,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>274859.77</v>
+        <v>274849.46000000002</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44290,7 +44303,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>289272.89</v>
+        <v>289262.58</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44332,7 +44345,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>301776.34000000003</v>
+        <v>301766.03000000003</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44374,7 +44387,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>314297.52</v>
+        <v>314287.21000000002</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44446,15 +44459,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>314297.52</v>
+        <v>314287.21000000002</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4702440.32</v>
+        <v>4702192.8800000008</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.219978318083832</v>
+        <v>97.217345865639061</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44501,12 +44514,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="380" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="379"/>
-      <c r="C3" s="379"/>
-      <c r="D3" s="380"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="382"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44652,12 +44665,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="381" t="s">
+      <c r="A13" s="383" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="382"/>
-      <c r="C13" s="382"/>
-      <c r="D13" s="383"/>
+      <c r="B13" s="384"/>
+      <c r="C13" s="384"/>
+      <c r="D13" s="385"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -44704,8 +44717,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="387"/>
-      <c r="H16" s="387"/>
+      <c r="G16" s="379"/>
+      <c r="H16" s="379"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44720,8 +44733,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="387"/>
-      <c r="H17" s="387"/>
+      <c r="G17" s="379"/>
+      <c r="H17" s="379"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44736,8 +44749,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="387"/>
-      <c r="H18" s="387"/>
+      <c r="G18" s="379"/>
+      <c r="H18" s="379"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44751,8 +44764,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="387"/>
-      <c r="H19" s="387"/>
+      <c r="G19" s="379"/>
+      <c r="H19" s="379"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44766,8 +44779,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="387"/>
-      <c r="H20" s="387"/>
+      <c r="G20" s="379"/>
+      <c r="H20" s="379"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44781,8 +44794,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="387"/>
-      <c r="H21" s="387"/>
+      <c r="G21" s="379"/>
+      <c r="H21" s="379"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -44807,9 +44820,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="384"/>
-      <c r="C23" s="385"/>
-      <c r="D23" s="386"/>
+      <c r="B23" s="386"/>
+      <c r="C23" s="387"/>
+      <c r="D23" s="388"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -44821,10 +44834,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="381"/>
-      <c r="B24" s="382"/>
-      <c r="C24" s="382"/>
-      <c r="D24" s="383"/>
+      <c r="A24" s="383"/>
+      <c r="B24" s="384"/>
+      <c r="C24" s="384"/>
+      <c r="D24" s="385"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -44937,9 +44950,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="384"/>
-      <c r="C34" s="385"/>
-      <c r="D34" s="386"/>
+      <c r="B34" s="386"/>
+      <c r="C34" s="387"/>
+      <c r="D34" s="388"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45072,17 +45085,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45090,19 +45103,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -45349,6 +45349,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -45359,17 +45372,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73CB8BEA-E38B-414E-AE6B-8CCC019FD87A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45388,6 +45390,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
   <ds:schemaRefs>

--- a/data/umr/Resumen UMR Abril 2026.xlsx
+++ b/data/umr/Resumen UMR Abril 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="41" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB082D29-6650-4481-A85D-4F336B809E1A}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A481F601-2057-42FD-9896-FCB8A6EEAC05}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Odometro-Kilometraje" sheetId="1" r:id="rId1"/>
@@ -4497,11 +4497,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4510,24 +4510,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4543,9 +4525,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4572,6 +4551,27 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4584,9 +4584,6 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4614,6 +4611,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -15364,14 +15364,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="359" t="s">
+      <c r="B2" s="368" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="360" t="s">
+      <c r="C2" s="368"/>
+      <c r="D2" s="369" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="360"/>
+      <c r="E2" s="369"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15456,59 +15456,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="359" t="s">
+      <c r="B3" s="368" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="359"/>
-      <c r="D3" s="360" t="s">
+      <c r="C3" s="368"/>
+      <c r="D3" s="369" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="360"/>
-      <c r="F3" s="355" t="s">
+      <c r="E3" s="369"/>
+      <c r="F3" s="350" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="355" t="s">
+      <c r="G3" s="350" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="355" t="s">
+      <c r="H3" s="350" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="355" t="s">
+      <c r="I3" s="350" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="355" t="s">
+      <c r="J3" s="350" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="355" t="s">
+      <c r="K3" s="350" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="355" t="s">
+      <c r="L3" s="350" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="355" t="s">
+      <c r="M3" s="350" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="366" t="s">
+      <c r="N3" s="351" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="366" t="s">
+      <c r="O3" s="351" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="365"/>
-      <c r="Q3" s="367" t="s">
+      <c r="P3" s="359"/>
+      <c r="Q3" s="360" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="368"/>
-      <c r="S3" s="369"/>
-      <c r="T3" s="370" t="s">
+      <c r="R3" s="361"/>
+      <c r="S3" s="362"/>
+      <c r="T3" s="363" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="371"/>
-      <c r="V3" s="372"/>
-      <c r="W3" s="363" t="s">
+      <c r="U3" s="364"/>
+      <c r="V3" s="365"/>
+      <c r="W3" s="357" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="363" t="s">
+      <c r="X3" s="357" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15526,17 +15526,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="355"/>
-      <c r="G4" s="356"/>
-      <c r="H4" s="356"/>
-      <c r="I4" s="355"/>
-      <c r="J4" s="355"/>
-      <c r="K4" s="355"/>
-      <c r="L4" s="355"/>
-      <c r="M4" s="355"/>
-      <c r="N4" s="366"/>
-      <c r="O4" s="366"/>
-      <c r="P4" s="365"/>
+      <c r="F4" s="350"/>
+      <c r="G4" s="370"/>
+      <c r="H4" s="370"/>
+      <c r="I4" s="350"/>
+      <c r="J4" s="350"/>
+      <c r="K4" s="350"/>
+      <c r="L4" s="350"/>
+      <c r="M4" s="350"/>
+      <c r="N4" s="351"/>
+      <c r="O4" s="351"/>
+      <c r="P4" s="359"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15555,8 +15555,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="364"/>
+      <c r="W4" s="358"/>
+      <c r="X4" s="358"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -16566,7 +16566,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="357" t="s">
+      <c r="A20" s="373" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="218">
@@ -16633,7 +16633,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="357"/>
+      <c r="A21" s="373"/>
       <c r="B21" s="218">
         <v>0</v>
       </c>
@@ -16698,7 +16698,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="357"/>
+      <c r="A22" s="373"/>
       <c r="B22" s="218">
         <v>0</v>
       </c>
@@ -16763,7 +16763,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="357"/>
+      <c r="A23" s="373"/>
       <c r="B23" s="218">
         <v>0</v>
       </c>
@@ -16828,7 +16828,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="357"/>
+      <c r="A24" s="373"/>
       <c r="B24" s="218">
         <v>0</v>
       </c>
@@ -17032,7 +17032,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="357" t="s">
+      <c r="A27" s="373" t="s">
         <v>181</v>
       </c>
       <c r="B27" s="218">
@@ -17099,7 +17099,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="357"/>
+      <c r="A28" s="373"/>
       <c r="B28" s="218">
         <v>0</v>
       </c>
@@ -17164,7 +17164,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="357"/>
+      <c r="A29" s="373"/>
       <c r="B29" s="218">
         <v>0</v>
       </c>
@@ -17229,7 +17229,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="357"/>
+      <c r="A30" s="373"/>
       <c r="B30" s="218">
         <v>0</v>
       </c>
@@ -17293,7 +17293,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="357"/>
+      <c r="A31" s="373"/>
       <c r="B31" s="218">
         <v>0</v>
       </c>
@@ -17962,7 +17962,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="358" t="s">
+      <c r="A41" s="374" t="s">
         <v>182</v>
       </c>
       <c r="B41" s="295">
@@ -18031,7 +18031,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="358"/>
+      <c r="A42" s="374"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -18105,7 +18105,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="358"/>
+      <c r="A43" s="374"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -18177,7 +18177,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="358"/>
+      <c r="A44" s="374"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -18249,7 +18249,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="358"/>
+      <c r="A45" s="374"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -18948,7 +18948,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="357" t="s">
+      <c r="A55" s="373" t="s">
         <v>183</v>
       </c>
       <c r="B55" s="295">
@@ -19019,7 +19019,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="357"/>
+      <c r="A56" s="373"/>
       <c r="B56" s="295">
         <v>33</v>
       </c>
@@ -19086,7 +19086,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="357"/>
+      <c r="A57" s="373"/>
       <c r="B57" s="295">
         <v>29</v>
       </c>
@@ -19154,7 +19154,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="357"/>
+      <c r="A58" s="373"/>
       <c r="B58" s="295">
         <v>0</v>
       </c>
@@ -19219,7 +19219,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="357"/>
+      <c r="A59" s="373"/>
       <c r="B59" s="295">
         <v>4</v>
       </c>
@@ -19952,12 +19952,14 @@
       <c r="Q69" s="186"/>
       <c r="R69" s="186"/>
       <c r="S69" s="217"/>
-      <c r="T69" s="183"/>
+      <c r="T69" s="183">
+        <v>3</v>
+      </c>
       <c r="U69" s="217"/>
       <c r="V69" s="229"/>
       <c r="W69" s="185">
         <f>J69-(T69*($M$2-$K$1)+(U69*($M$2-$M$1))+(V69*($U$2)))</f>
-        <v>5261.8600000000006</v>
+        <v>5208.670000000001</v>
       </c>
       <c r="X69" s="182">
         <f>H69*$M$2</f>
@@ -20282,7 +20284,7 @@
       </c>
       <c r="O74" s="21">
         <f>(W74/N74)*100</f>
-        <v>97.018365472910943</v>
+        <v>96.611340679522513</v>
       </c>
       <c r="P74" s="192"/>
       <c r="Q74" s="181"/>
@@ -20293,7 +20295,7 @@
       <c r="V74" s="181"/>
       <c r="W74" s="193">
         <f>SUM(W68:W73)</f>
-        <v>12678.360000000002</v>
+        <v>12625.170000000002</v>
       </c>
       <c r="X74" s="193">
         <f>SUM(X68:X73)</f>
@@ -25564,7 +25566,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="358" t="s">
+      <c r="A153" s="374" t="s">
         <v>186</v>
       </c>
       <c r="B153" s="295">
@@ -25635,7 +25637,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="358"/>
+      <c r="A154" s="374"/>
       <c r="B154" s="295">
         <v>33</v>
       </c>
@@ -25704,7 +25706,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="358"/>
+      <c r="A155" s="374"/>
       <c r="B155" s="295">
         <v>29</v>
       </c>
@@ -25771,7 +25773,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="358"/>
+      <c r="A156" s="374"/>
       <c r="B156" s="295">
         <v>0</v>
       </c>
@@ -25838,7 +25840,7 @@
       <c r="Z156" s="124"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="358"/>
+      <c r="A157" s="374"/>
       <c r="B157" s="295">
         <v>4</v>
       </c>
@@ -29950,21 +29952,21 @@
       <c r="L223" s="353"/>
       <c r="M223" s="353"/>
       <c r="N223" s="354"/>
-      <c r="P223" s="373" t="s">
+      <c r="P223" s="366" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="373"/>
-      <c r="R223" s="373"/>
-      <c r="S223" s="374"/>
-      <c r="T223" s="370" t="s">
+      <c r="Q223" s="366"/>
+      <c r="R223" s="366"/>
+      <c r="S223" s="367"/>
+      <c r="T223" s="363" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="371"/>
-      <c r="V223" s="372"/>
-      <c r="W223" s="361" t="s">
+      <c r="U223" s="364"/>
+      <c r="V223" s="365"/>
+      <c r="W223" s="355" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="361" t="s">
+      <c r="X223" s="355" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30030,8 +30032,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="362"/>
-      <c r="X224" s="362"/>
+      <c r="W224" s="356"/>
+      <c r="X224" s="356"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30105,7 +30107,7 @@
       </c>
       <c r="T225" s="209">
         <f>SUM(T194,T187,T180,T173,T166,T159,T152,T145,T138,T131,T124,T117,T110,T103,T96,T89,T82,T75,T68,T61,T54,T47,T40,T33,T26,T19,T12,T5,T201,T208,T215)+T6+T13+T20+T27+T34+T41+T48+T55+T62+T69+T76+T83+T90+T97+T104+T111+T118+T125+T132+T139+T146+T153+T160+T167+T174+T181+T188+T195+T202+T209+T216</f>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="U225" s="209">
         <f>SUM(U194,U187,U180,U173,U166,U159,U152,U145,U138,U131,U124,U117,U110,U103,U96,U89,U82,U75,U68,U61,U54,U47,U40,U33,U26,U19,U12,U5,U201,U208,U216)</f>
@@ -30117,7 +30119,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>314287.21000000002</v>
+        <v>314234.02</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -30583,10 +30585,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="350" t="s">
+      <c r="B237" s="371" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="351"/>
+      <c r="C237" s="372"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -30762,13 +30764,20 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A153:A157"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:H4"/>
     <mergeCell ref="X223:X224"/>
     <mergeCell ref="W223:W224"/>
     <mergeCell ref="W3:W4"/>
@@ -30779,20 +30788,13 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="P223:S223"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A153:A157"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D194:E199 D187:E192 D180:E185 D173:E178 D166:E171 D159:E164">
     <cfRule type="expression" dxfId="39" priority="134">
@@ -39374,6 +39376,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -39390,21 +39407,6 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -41298,7 +41300,7 @@
       </c>
       <c r="L20" s="83">
         <f>'KM-Servicio'!T69</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="83">
         <f>'KM-Servicio'!T76</f>
@@ -42024,7 +42026,7 @@
       </c>
       <c r="B29" s="226">
         <f t="shared" si="0"/>
-        <v>314301.23</v>
+        <v>314248.03999999998</v>
       </c>
       <c r="C29" s="91">
         <f>(C12*$B$12+C13*$B$13+C14*$B$14+C15*$B$15+C17*$B$17+C20*$B$20+C16*$B$16+C19*$B$19+C22*$B$22+C23*$B$23+C21*B21)</f>
@@ -42064,7 +42066,7 @@
       </c>
       <c r="L29" s="91">
         <f>(L12*$B$12+L13*$B$13+L14*$B$14+L15*$B$15+L17*$B$17+L20*$B$20+L16*$B$16+L19*$B$19+L21*$B$21+L22*$B$22+L24*B24)</f>
-        <v>12678.360000000002</v>
+        <v>12625.170000000002</v>
       </c>
       <c r="M29" s="91">
         <f>(M12*$B$12+M13*$B$13+M14*$B$14+M15*$B$15+M17*$B$17+M20*$B$20+M16*$B$16+M19*$B$19+M21*$B$21+M22*$B$22+M24*B24)</f>
@@ -42282,7 +42284,7 @@
       </c>
       <c r="B31" s="226">
         <f t="shared" si="0"/>
-        <v>32687327.920000006</v>
+        <v>32681796.160000004</v>
       </c>
       <c r="C31" s="91">
         <f t="shared" ref="C31:AD31" si="12">C29*104</f>
@@ -42322,7 +42324,7 @@
       </c>
       <c r="L31" s="91">
         <f t="shared" si="12"/>
-        <v>1318549.4400000002</v>
+        <v>1313017.6800000002</v>
       </c>
       <c r="M31" s="91">
         <f t="shared" si="12"/>
@@ -42411,7 +42413,7 @@
       </c>
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>628602.46</v>
+        <v>628496.07999999996</v>
       </c>
       <c r="C32" s="91">
         <f>C29*2</f>
@@ -42451,7 +42453,7 @@
       </c>
       <c r="L32" s="91">
         <f t="shared" si="15"/>
-        <v>25356.720000000005</v>
+        <v>25250.340000000004</v>
       </c>
       <c r="M32" s="91">
         <f t="shared" si="15"/>
@@ -42669,7 +42671,7 @@
       </c>
       <c r="B34" s="226">
         <f t="shared" si="0"/>
-        <v>24924087.539000005</v>
+        <v>24919869.572000004</v>
       </c>
       <c r="C34" s="91">
         <f>C29*79.3</f>
@@ -42709,7 +42711,7 @@
       </c>
       <c r="L34" s="91">
         <f t="shared" si="21"/>
-        <v>1005393.9480000002</v>
+        <v>1001175.9810000001</v>
       </c>
       <c r="M34" s="91">
         <f t="shared" si="21"/>
@@ -43544,15 +43546,15 @@
       </c>
       <c r="D13" s="341">
         <f>'KM-Servicio'!W74</f>
-        <v>12678.360000000002</v>
+        <v>12625.170000000002</v>
       </c>
       <c r="E13" s="12">
         <f t="shared" si="1"/>
-        <v>102133.52</v>
+        <v>102080.33</v>
       </c>
       <c r="F13" s="166">
         <f>'KM-Servicio'!O74</f>
-        <v>97.018365472910943</v>
+        <v>96.611340679522513</v>
       </c>
       <c r="G13" s="167">
         <f>SUM('KM-Servicio'!B74:C74)</f>
@@ -43564,7 +43566,7 @@
       </c>
       <c r="I13" s="12">
         <f>'Oferta Diaria'!L34</f>
-        <v>1005393.9480000002</v>
+        <v>1001175.9810000001</v>
       </c>
       <c r="J13" s="161" t="s">
         <v>137</v>
@@ -43590,7 +43592,7 @@
       </c>
       <c r="E14" s="12">
         <f t="shared" si="1"/>
-        <v>108603.02</v>
+        <v>108549.83</v>
       </c>
       <c r="F14" s="166">
         <f>'KM-Servicio'!O81</f>
@@ -43632,7 +43634,7 @@
       </c>
       <c r="E15" s="12">
         <f t="shared" si="1"/>
-        <v>113519.84000000001</v>
+        <v>113466.65000000001</v>
       </c>
       <c r="F15" s="166">
         <f>'KM-Servicio'!O88</f>
@@ -43674,7 +43676,7 @@
       </c>
       <c r="E16" s="312">
         <f t="shared" si="1"/>
-        <v>125972.49000000002</v>
+        <v>125919.30000000002</v>
       </c>
       <c r="F16" s="313">
         <f>'KM-Servicio'!O95</f>
@@ -43716,7 +43718,7 @@
       </c>
       <c r="E17" s="312">
         <f t="shared" si="1"/>
-        <v>138546.86000000002</v>
+        <v>138493.67000000001</v>
       </c>
       <c r="F17" s="313">
         <f>'KM-Servicio'!O102</f>
@@ -43758,7 +43760,7 @@
       </c>
       <c r="E18" s="12">
         <f t="shared" si="1"/>
-        <v>151099.79</v>
+        <v>151046.6</v>
       </c>
       <c r="F18" s="166">
         <f>'KM-Servicio'!O109</f>
@@ -43800,7 +43802,7 @@
       </c>
       <c r="E19" s="12">
         <f t="shared" si="1"/>
-        <v>163745.08000000002</v>
+        <v>163691.89000000001</v>
       </c>
       <c r="F19" s="166">
         <f>'KM-Servicio'!O116</f>
@@ -43841,7 +43843,7 @@
       </c>
       <c r="E20" s="12">
         <f t="shared" si="1"/>
-        <v>176280.28000000003</v>
+        <v>176227.09000000003</v>
       </c>
       <c r="F20" s="166">
         <f>'KM-Servicio'!O123</f>
@@ -43883,7 +43885,7 @@
       </c>
       <c r="E21" s="12">
         <f t="shared" si="1"/>
-        <v>182749.78000000003</v>
+        <v>182696.59000000003</v>
       </c>
       <c r="F21" s="166">
         <f>'KM-Servicio'!O130</f>
@@ -43925,7 +43927,7 @@
       </c>
       <c r="E22" s="12">
         <f t="shared" si="1"/>
-        <v>187752.86000000002</v>
+        <v>187699.67</v>
       </c>
       <c r="F22" s="171">
         <f>'KM-Servicio'!O137</f>
@@ -43967,7 +43969,7 @@
       </c>
       <c r="E23" s="312">
         <f t="shared" si="1"/>
-        <v>200342.57</v>
+        <v>200289.38</v>
       </c>
       <c r="F23" s="313">
         <f>'KM-Servicio'!O144</f>
@@ -44009,7 +44011,7 @@
       </c>
       <c r="E24" s="312">
         <f t="shared" si="1"/>
-        <v>212777.49000000002</v>
+        <v>212724.30000000002</v>
       </c>
       <c r="F24" s="313">
         <f>'KM-Servicio'!O151</f>
@@ -44051,7 +44053,7 @@
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>225572.54</v>
+        <v>225519.35</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
@@ -44093,7 +44095,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>238075.99000000002</v>
+        <v>238022.80000000002</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44135,7 +44137,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>250480.48</v>
+        <v>250427.29</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44177,7 +44179,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>256949.98</v>
+        <v>256896.79</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44219,7 +44221,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>261866.80000000002</v>
+        <v>261813.61000000002</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44261,7 +44263,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>274849.46000000002</v>
+        <v>274796.27</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44303,7 +44305,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>289262.58</v>
+        <v>289209.39</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44345,7 +44347,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>301766.03000000003</v>
+        <v>301712.84000000003</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44387,7 +44389,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>314287.21000000002</v>
+        <v>314234.02</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44459,15 +44461,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>314287.21000000002</v>
+        <v>314234.02</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4702192.8800000008</v>
+        <v>4701075.8900000006</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.217345865639061</v>
+        <v>97.203778372526102</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44479,7 +44481,7 @@
       </c>
       <c r="I36" s="169">
         <f>SUM(I4:I34)</f>
-        <v>24924087.539000005</v>
+        <v>24919869.572000004</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="168"/>
@@ -44514,12 +44516,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="379" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="381"/>
-      <c r="C3" s="381"/>
-      <c r="D3" s="382"/>
+      <c r="B3" s="380"/>
+      <c r="C3" s="380"/>
+      <c r="D3" s="381"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44665,12 +44667,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="383" t="s">
+      <c r="A13" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="384"/>
-      <c r="C13" s="384"/>
-      <c r="D13" s="385"/>
+      <c r="B13" s="383"/>
+      <c r="C13" s="383"/>
+      <c r="D13" s="384"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -44717,8 +44719,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="379"/>
-      <c r="H16" s="379"/>
+      <c r="G16" s="388"/>
+      <c r="H16" s="388"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44733,8 +44735,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="379"/>
-      <c r="H17" s="379"/>
+      <c r="G17" s="388"/>
+      <c r="H17" s="388"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44749,8 +44751,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="379"/>
-      <c r="H18" s="379"/>
+      <c r="G18" s="388"/>
+      <c r="H18" s="388"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44764,8 +44766,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="379"/>
-      <c r="H19" s="379"/>
+      <c r="G19" s="388"/>
+      <c r="H19" s="388"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44779,8 +44781,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="379"/>
-      <c r="H20" s="379"/>
+      <c r="G20" s="388"/>
+      <c r="H20" s="388"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44794,8 +44796,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="379"/>
-      <c r="H21" s="379"/>
+      <c r="G21" s="388"/>
+      <c r="H21" s="388"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -44820,9 +44822,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="386"/>
-      <c r="C23" s="387"/>
-      <c r="D23" s="388"/>
+      <c r="B23" s="385"/>
+      <c r="C23" s="386"/>
+      <c r="D23" s="387"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -44834,10 +44836,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="383"/>
-      <c r="B24" s="384"/>
-      <c r="C24" s="384"/>
-      <c r="D24" s="385"/>
+      <c r="A24" s="382"/>
+      <c r="B24" s="383"/>
+      <c r="C24" s="383"/>
+      <c r="D24" s="384"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -44950,9 +44952,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="386"/>
-      <c r="C34" s="387"/>
-      <c r="D34" s="388"/>
+      <c r="B34" s="385"/>
+      <c r="C34" s="386"/>
+      <c r="D34" s="387"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45085,17 +45087,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45103,6 +45105,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -45349,29 +45373,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73CB8BEA-E38B-414E-AE6B-8CCC019FD87A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -45388,23 +45409,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/umr/Resumen UMR Abril 2026.xlsx
+++ b/data/umr/Resumen UMR Abril 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="43" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A481F601-2057-42FD-9896-FCB8A6EEAC05}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="14_{697CB830-6CF5-47D5-8D68-0FE4753D0F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCD14F60-3B1F-4ED1-9048-B9716304977A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="686" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4497,11 +4497,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4510,6 +4510,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="47" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="52" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4525,6 +4543,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="76" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="51" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4551,27 +4572,6 @@
     <xf numFmtId="0" fontId="14" fillId="51" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -4584,6 +4584,9 @@
     </xf>
     <xf numFmtId="49" fontId="42" fillId="44" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4611,9 +4614,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="84">
@@ -14466,19 +14466,19 @@
         <v>13218</v>
       </c>
       <c r="R87" s="16">
-        <f t="shared" ref="R87:AB87" si="71">SUM(R51:R85)</f>
+        <f>SUM(R51:R85)</f>
         <v>13045</v>
       </c>
       <c r="S87" s="16">
-        <f t="shared" si="71"/>
+        <f>SUM(S51:S85)</f>
         <v>6533</v>
       </c>
       <c r="T87" s="16">
-        <f t="shared" si="71"/>
+        <f>SUM(T51:T85)</f>
         <v>5071</v>
       </c>
       <c r="U87" s="16">
-        <f t="shared" si="71"/>
+        <f>SUM(U51:U85)</f>
         <v>13134</v>
       </c>
       <c r="V87" s="16">
@@ -14494,7 +14494,7 @@
         <v>12975</v>
       </c>
       <c r="Y87" s="16">
-        <f t="shared" si="71"/>
+        <f t="shared" ref="R87:AB87" si="71">SUM(Y51:Y85)</f>
         <v>12821</v>
       </c>
       <c r="Z87" s="16">
@@ -15174,60 +15174,25 @@
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AC95" s="346">
-        <f>3*'KM-Servicio'!$M$1+2*4.82</f>
-        <v>96.97</v>
-      </c>
-      <c r="AD95" s="344">
-        <f>43.13+18.83</f>
-        <v>61.96</v>
-      </c>
-      <c r="AE95" s="344">
-        <f>43.13+18.83</f>
-        <v>61.96</v>
-      </c>
+      <c r="R95" s="172"/>
+      <c r="AC95" s="346"/>
+      <c r="AD95" s="344"/>
+      <c r="AE95" s="344"/>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AC96" s="346">
-        <f>3*'KM-Servicio'!$M$1+2*4.82</f>
-        <v>96.97</v>
-      </c>
-      <c r="AD96" s="344">
-        <f>43.13+18.83</f>
-        <v>61.96</v>
-      </c>
-      <c r="AE96" s="344">
-        <f>43.13+18.83</f>
-        <v>61.96</v>
-      </c>
+      <c r="AC96" s="346"/>
+      <c r="AD96" s="344"/>
+      <c r="AE96" s="344"/>
     </row>
     <row r="97" spans="29:31" x14ac:dyDescent="0.25">
-      <c r="AC97" s="345">
-        <f>AC95+AC96</f>
-        <v>193.94</v>
-      </c>
-      <c r="AD97" s="345">
-        <f>AD95+AD96</f>
-        <v>123.92</v>
-      </c>
-      <c r="AE97" s="345">
-        <f>AE95+AE96</f>
-        <v>123.92</v>
-      </c>
+      <c r="AC97" s="345"/>
+      <c r="AD97" s="345"/>
+      <c r="AE97" s="345"/>
     </row>
     <row r="98" spans="29:31" x14ac:dyDescent="0.25">
-      <c r="AC98" s="345">
-        <f>AC91-AC97</f>
-        <v>104.06</v>
-      </c>
-      <c r="AD98" s="345">
-        <f>AD91-AD97</f>
-        <v>62.08</v>
-      </c>
-      <c r="AE98" s="345">
-        <f>AE91-AE97</f>
-        <v>41.08</v>
-      </c>
+      <c r="AC98" s="345"/>
+      <c r="AD98" s="345"/>
+      <c r="AE98" s="345"/>
     </row>
   </sheetData>
   <dataConsolidate>
@@ -15243,6 +15208,9 @@
   <phoneticPr fontId="54" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
+  <ignoredErrors>
+    <ignoredError sqref="J89" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -15364,14 +15332,14 @@
     </row>
     <row r="2" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
-      <c r="B2" s="368" t="s">
+      <c r="B2" s="359" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="368"/>
-      <c r="D2" s="369" t="s">
+      <c r="C2" s="359"/>
+      <c r="D2" s="360" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="369"/>
+      <c r="E2" s="360"/>
       <c r="F2" s="232" t="s">
         <v>163</v>
       </c>
@@ -15456,59 +15424,59 @@
     </row>
     <row r="3" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
-      <c r="B3" s="368" t="s">
+      <c r="B3" s="359" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="368"/>
-      <c r="D3" s="369" t="s">
+      <c r="C3" s="359"/>
+      <c r="D3" s="360" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="369"/>
-      <c r="F3" s="350" t="s">
+      <c r="E3" s="360"/>
+      <c r="F3" s="355" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="350" t="s">
+      <c r="G3" s="355" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="350" t="s">
+      <c r="H3" s="355" t="s">
         <v>161</v>
       </c>
-      <c r="I3" s="350" t="s">
+      <c r="I3" s="355" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="350" t="s">
+      <c r="J3" s="355" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="350" t="s">
+      <c r="K3" s="355" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="350" t="s">
+      <c r="L3" s="355" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="350" t="s">
+      <c r="M3" s="355" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="351" t="s">
+      <c r="N3" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="351" t="s">
+      <c r="O3" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="359"/>
-      <c r="Q3" s="360" t="s">
+      <c r="P3" s="365"/>
+      <c r="Q3" s="367" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="361"/>
-      <c r="S3" s="362"/>
-      <c r="T3" s="363" t="s">
+      <c r="R3" s="368"/>
+      <c r="S3" s="369"/>
+      <c r="T3" s="370" t="s">
         <v>142</v>
       </c>
-      <c r="U3" s="364"/>
-      <c r="V3" s="365"/>
-      <c r="W3" s="357" t="s">
+      <c r="U3" s="371"/>
+      <c r="V3" s="372"/>
+      <c r="W3" s="363" t="s">
         <v>143</v>
       </c>
-      <c r="X3" s="357" t="s">
+      <c r="X3" s="363" t="s">
         <v>162</v>
       </c>
     </row>
@@ -15526,17 +15494,17 @@
       <c r="E4" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="350"/>
-      <c r="G4" s="370"/>
-      <c r="H4" s="370"/>
-      <c r="I4" s="350"/>
-      <c r="J4" s="350"/>
-      <c r="K4" s="350"/>
-      <c r="L4" s="350"/>
-      <c r="M4" s="350"/>
-      <c r="N4" s="351"/>
-      <c r="O4" s="351"/>
-      <c r="P4" s="359"/>
+      <c r="F4" s="355"/>
+      <c r="G4" s="356"/>
+      <c r="H4" s="356"/>
+      <c r="I4" s="355"/>
+      <c r="J4" s="355"/>
+      <c r="K4" s="355"/>
+      <c r="L4" s="355"/>
+      <c r="M4" s="355"/>
+      <c r="N4" s="366"/>
+      <c r="O4" s="366"/>
+      <c r="P4" s="365"/>
       <c r="Q4" s="194" t="s">
         <v>140</v>
       </c>
@@ -15555,8 +15523,8 @@
       <c r="V4" s="236" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="358"/>
-      <c r="X4" s="358"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="364"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
@@ -16566,7 +16534,7 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="373" t="s">
+      <c r="A20" s="357" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="218">
@@ -16633,7 +16601,7 @@
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="373"/>
+      <c r="A21" s="357"/>
       <c r="B21" s="218">
         <v>0</v>
       </c>
@@ -16698,7 +16666,7 @@
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="373"/>
+      <c r="A22" s="357"/>
       <c r="B22" s="218">
         <v>0</v>
       </c>
@@ -16763,7 +16731,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="373"/>
+      <c r="A23" s="357"/>
       <c r="B23" s="218">
         <v>0</v>
       </c>
@@ -16828,7 +16796,7 @@
       </c>
     </row>
     <row r="24" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="373"/>
+      <c r="A24" s="357"/>
       <c r="B24" s="218">
         <v>0</v>
       </c>
@@ -17032,7 +17000,7 @@
       </c>
     </row>
     <row r="27" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="373" t="s">
+      <c r="A27" s="357" t="s">
         <v>181</v>
       </c>
       <c r="B27" s="218">
@@ -17099,7 +17067,7 @@
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="373"/>
+      <c r="A28" s="357"/>
       <c r="B28" s="218">
         <v>0</v>
       </c>
@@ -17164,7 +17132,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="373"/>
+      <c r="A29" s="357"/>
       <c r="B29" s="218">
         <v>0</v>
       </c>
@@ -17229,7 +17197,7 @@
       </c>
     </row>
     <row r="30" spans="1:24" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="373"/>
+      <c r="A30" s="357"/>
       <c r="B30" s="218">
         <v>0</v>
       </c>
@@ -17293,7 +17261,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="373"/>
+      <c r="A31" s="357"/>
       <c r="B31" s="218">
         <v>0</v>
       </c>
@@ -17962,7 +17930,7 @@
       </c>
     </row>
     <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="374" t="s">
+      <c r="A41" s="358" t="s">
         <v>182</v>
       </c>
       <c r="B41" s="295">
@@ -18031,7 +17999,7 @@
       </c>
     </row>
     <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="374"/>
+      <c r="A42" s="358"/>
       <c r="B42" s="295">
         <v>33</v>
       </c>
@@ -18105,7 +18073,7 @@
       <c r="AF42" s="255"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A43" s="374"/>
+      <c r="A43" s="358"/>
       <c r="B43" s="295">
         <v>29</v>
       </c>
@@ -18177,7 +18145,7 @@
       <c r="AF43" s="255"/>
     </row>
     <row r="44" spans="1:32" s="124" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="374"/>
+      <c r="A44" s="358"/>
       <c r="B44" s="295">
         <v>0</v>
       </c>
@@ -18249,7 +18217,7 @@
       <c r="AF44" s="255"/>
     </row>
     <row r="45" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="374"/>
+      <c r="A45" s="358"/>
       <c r="B45" s="295">
         <v>4</v>
       </c>
@@ -18948,7 +18916,7 @@
       </c>
     </row>
     <row r="55" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="373" t="s">
+      <c r="A55" s="357" t="s">
         <v>183</v>
       </c>
       <c r="B55" s="295">
@@ -19019,7 +18987,7 @@
       </c>
     </row>
     <row r="56" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="373"/>
+      <c r="A56" s="357"/>
       <c r="B56" s="295">
         <v>33</v>
       </c>
@@ -19086,7 +19054,7 @@
       </c>
     </row>
     <row r="57" spans="1:65" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="373"/>
+      <c r="A57" s="357"/>
       <c r="B57" s="295">
         <v>29</v>
       </c>
@@ -19154,7 +19122,7 @@
       </c>
     </row>
     <row r="58" spans="1:65" s="124" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="373"/>
+      <c r="A58" s="357"/>
       <c r="B58" s="295">
         <v>0</v>
       </c>
@@ -19219,7 +19187,7 @@
       </c>
     </row>
     <row r="59" spans="1:65" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="373"/>
+      <c r="A59" s="357"/>
       <c r="B59" s="295">
         <v>4</v>
       </c>
@@ -25566,7 +25534,7 @@
       </c>
     </row>
     <row r="153" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="374" t="s">
+      <c r="A153" s="358" t="s">
         <v>186</v>
       </c>
       <c r="B153" s="295">
@@ -25637,7 +25605,7 @@
       <c r="Z153" s="124"/>
     </row>
     <row r="154" spans="1:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="374"/>
+      <c r="A154" s="358"/>
       <c r="B154" s="295">
         <v>33</v>
       </c>
@@ -25706,7 +25674,7 @@
       <c r="Z154" s="124"/>
     </row>
     <row r="155" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="374"/>
+      <c r="A155" s="358"/>
       <c r="B155" s="295">
         <v>29</v>
       </c>
@@ -25758,12 +25726,14 @@
       <c r="Q155" s="189"/>
       <c r="R155" s="189"/>
       <c r="S155" s="189"/>
-      <c r="T155" s="189"/>
+      <c r="T155" s="189">
+        <v>1</v>
+      </c>
       <c r="U155" s="189"/>
       <c r="V155" s="189"/>
       <c r="W155" s="182">
-        <f>J155</f>
-        <v>989.74</v>
+        <f>J155-AH1</f>
+        <v>975.72</v>
       </c>
       <c r="X155" s="182">
         <f>H155*$M$1</f>
@@ -25773,7 +25743,7 @@
       <c r="Z155" s="124"/>
     </row>
     <row r="156" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="374"/>
+      <c r="A156" s="358"/>
       <c r="B156" s="295">
         <v>0</v>
       </c>
@@ -25840,7 +25810,7 @@
       <c r="Z156" s="124"/>
     </row>
     <row r="157" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="374"/>
+      <c r="A157" s="358"/>
       <c r="B157" s="295">
         <v>4</v>
       </c>
@@ -25957,7 +25927,7 @@
       </c>
       <c r="O158" s="21">
         <f>(W158/N158)*100</f>
-        <v>97.152999240698563</v>
+        <v>97.046545178435835</v>
       </c>
       <c r="P158" s="192"/>
       <c r="Q158" s="181"/>
@@ -25968,7 +25938,7 @@
       <c r="V158" s="181"/>
       <c r="W158" s="193">
         <f>SUM(W152:W157)</f>
-        <v>12795.050000000001</v>
+        <v>12781.03</v>
       </c>
       <c r="X158" s="193">
         <f>SUM(X152:X157)</f>
@@ -29952,21 +29922,21 @@
       <c r="L223" s="353"/>
       <c r="M223" s="353"/>
       <c r="N223" s="354"/>
-      <c r="P223" s="366" t="s">
+      <c r="P223" s="373" t="s">
         <v>139</v>
       </c>
-      <c r="Q223" s="366"/>
-      <c r="R223" s="366"/>
-      <c r="S223" s="367"/>
-      <c r="T223" s="363" t="s">
+      <c r="Q223" s="373"/>
+      <c r="R223" s="373"/>
+      <c r="S223" s="374"/>
+      <c r="T223" s="370" t="s">
         <v>142</v>
       </c>
-      <c r="U223" s="364"/>
-      <c r="V223" s="365"/>
-      <c r="W223" s="355" t="s">
+      <c r="U223" s="371"/>
+      <c r="V223" s="372"/>
+      <c r="W223" s="361" t="s">
         <v>143</v>
       </c>
-      <c r="X223" s="355" t="s">
+      <c r="X223" s="361" t="s">
         <v>162</v>
       </c>
     </row>
@@ -30032,8 +30002,8 @@
       <c r="V224" s="227" t="s">
         <v>146</v>
       </c>
-      <c r="W224" s="356"/>
-      <c r="X224" s="356"/>
+      <c r="W224" s="362"/>
+      <c r="X224" s="362"/>
     </row>
     <row r="225" spans="1:29" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="23" t="s">
@@ -30119,7 +30089,7 @@
       </c>
       <c r="W225" s="231">
         <f>W11+W18+W25+W32+W39+W46+W53+W60+W67+W74+W81+W88+W95+W102+W109+W116+W123+W130+W137+W144+W151+W158+W165+W172+W179+W186+W193+W200+W207+W214+W221</f>
-        <v>314234.02</v>
+        <v>314220</v>
       </c>
       <c r="X225" s="231">
         <f>X11+X18+X25+X32+X39+X46+X53+X60+X67+X74+X81+X88+X95+X102+X109+X116+X123+X130+X137+X144+X151+X158+X165+X172+X179+X186+X193+X200+X207+X214+X221</f>
@@ -30585,10 +30555,10 @@
     </row>
     <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="24"/>
-      <c r="B237" s="371" t="s">
+      <c r="B237" s="350" t="s">
         <v>55</v>
       </c>
-      <c r="C237" s="372"/>
+      <c r="C237" s="351"/>
       <c r="D237" s="25" t="s">
         <v>65</v>
       </c>
@@ -30764,20 +30734,13 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="31">
-    <mergeCell ref="B237:C237"/>
-    <mergeCell ref="B223:G223"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A153:A157"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="I223:N223"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="J3:J4"/>
     <mergeCell ref="X223:X224"/>
     <mergeCell ref="W223:W224"/>
     <mergeCell ref="W3:W4"/>
@@ -30788,13 +30751,20 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="X3:X4"/>
     <mergeCell ref="P223:S223"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="I223:N223"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="B237:C237"/>
+    <mergeCell ref="B223:G223"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A153:A157"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:E38 D194:E199 D187:E192 D180:E185 D173:E178 D166:E171 D159:E164">
     <cfRule type="expression" dxfId="39" priority="134">
@@ -39376,21 +39346,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="X1:Y1"/>
     <mergeCell ref="BH1:BI1"/>
     <mergeCell ref="BJ1:BK1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -39407,6 +39362,21 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AZ1:BA1"/>
     <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="X1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -44049,15 +44019,15 @@
       </c>
       <c r="D25" s="341">
         <f>'KM-Servicio'!$W$158</f>
-        <v>12795.050000000001</v>
+        <v>12781.03</v>
       </c>
       <c r="E25" s="12">
         <f t="shared" si="1"/>
-        <v>225519.35</v>
+        <v>225505.33000000002</v>
       </c>
       <c r="F25" s="166">
         <f>'KM-Servicio'!O158</f>
-        <v>97.152999240698563</v>
+        <v>97.046545178435835</v>
       </c>
       <c r="G25" s="167">
         <f>SUM('KM-Servicio'!B158:C158)</f>
@@ -44095,7 +44065,7 @@
       </c>
       <c r="E26" s="12">
         <f t="shared" si="1"/>
-        <v>238022.80000000002</v>
+        <v>238008.78000000003</v>
       </c>
       <c r="F26" s="166">
         <f>'KM-Servicio'!O165</f>
@@ -44137,7 +44107,7 @@
       </c>
       <c r="E27" s="12">
         <f t="shared" si="1"/>
-        <v>250427.29</v>
+        <v>250413.27000000002</v>
       </c>
       <c r="F27" s="166">
         <f>'KM-Servicio'!O172</f>
@@ -44179,7 +44149,7 @@
       </c>
       <c r="E28" s="312">
         <f t="shared" si="1"/>
-        <v>256896.79</v>
+        <v>256882.77000000002</v>
       </c>
       <c r="F28" s="313">
         <f>'KM-Servicio'!O179</f>
@@ -44221,7 +44191,7 @@
       </c>
       <c r="E29" s="12">
         <f t="shared" si="1"/>
-        <v>261813.61000000002</v>
+        <v>261799.59000000003</v>
       </c>
       <c r="F29" s="166">
         <f>'KM-Servicio'!O186</f>
@@ -44263,7 +44233,7 @@
       </c>
       <c r="E30" s="312">
         <f t="shared" si="1"/>
-        <v>274796.27</v>
+        <v>274782.25</v>
       </c>
       <c r="F30" s="313">
         <f>'KM-Servicio'!O193</f>
@@ -44305,7 +44275,7 @@
       </c>
       <c r="E31" s="312">
         <f t="shared" si="1"/>
-        <v>289209.39</v>
+        <v>289195.37</v>
       </c>
       <c r="F31" s="313">
         <f>'KM-Servicio'!O200</f>
@@ -44347,7 +44317,7 @@
       </c>
       <c r="E32" s="312">
         <f t="shared" si="1"/>
-        <v>301712.84000000003</v>
+        <v>301698.82</v>
       </c>
       <c r="F32" s="313">
         <f>'KM-Servicio'!O207</f>
@@ -44389,7 +44359,7 @@
       </c>
       <c r="E33" s="312">
         <f t="shared" si="1"/>
-        <v>314234.02</v>
+        <v>314220</v>
       </c>
       <c r="F33" s="166">
         <f>'KM-Servicio'!O46</f>
@@ -44461,15 +44431,15 @@
       </c>
       <c r="D36" s="169">
         <f>SUM(D4:D34)</f>
-        <v>314234.02</v>
+        <v>314220</v>
       </c>
       <c r="E36" s="169">
         <f>SUM(E4:E34)</f>
-        <v>4701075.8900000006</v>
+        <v>4700949.71</v>
       </c>
       <c r="F36" s="170">
         <f>AVERAGE(F4:F34)</f>
-        <v>97.203778372526102</v>
+        <v>97.20022990378402</v>
       </c>
       <c r="G36" s="169">
         <f>SUM(G4:G34)</f>
@@ -44516,12 +44486,12 @@
   <sheetData>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="379" t="s">
+      <c r="A3" s="380" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="381"/>
+      <c r="B3" s="381"/>
+      <c r="C3" s="381"/>
+      <c r="D3" s="382"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="96" t="s">
@@ -44667,12 +44637,12 @@
       <c r="J12" s="101"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="382" t="s">
+      <c r="A13" s="383" t="s">
         <v>109</v>
       </c>
-      <c r="B13" s="383"/>
-      <c r="C13" s="383"/>
-      <c r="D13" s="384"/>
+      <c r="B13" s="384"/>
+      <c r="C13" s="384"/>
+      <c r="D13" s="385"/>
       <c r="F13" s="140"/>
       <c r="G13" s="141"/>
       <c r="H13" s="141"/>
@@ -44719,8 +44689,8 @@
       <c r="C16" s="106"/>
       <c r="D16" s="107"/>
       <c r="F16" s="140"/>
-      <c r="G16" s="388"/>
-      <c r="H16" s="388"/>
+      <c r="G16" s="379"/>
+      <c r="H16" s="379"/>
       <c r="I16" s="140"/>
       <c r="J16" s="140"/>
       <c r="K16" s="140"/>
@@ -44735,8 +44705,8 @@
       <c r="C17" s="106"/>
       <c r="D17" s="107"/>
       <c r="F17" s="140"/>
-      <c r="G17" s="388"/>
-      <c r="H17" s="388"/>
+      <c r="G17" s="379"/>
+      <c r="H17" s="379"/>
       <c r="I17" s="140"/>
       <c r="J17" s="141"/>
       <c r="K17" s="141"/>
@@ -44751,8 +44721,8 @@
       <c r="C18" s="106"/>
       <c r="D18" s="107"/>
       <c r="F18" s="140"/>
-      <c r="G18" s="388"/>
-      <c r="H18" s="388"/>
+      <c r="G18" s="379"/>
+      <c r="H18" s="379"/>
       <c r="I18" s="141"/>
       <c r="J18" s="141"/>
       <c r="K18" s="43"/>
@@ -44766,8 +44736,8 @@
       <c r="C19" s="111"/>
       <c r="D19" s="107"/>
       <c r="F19" s="140"/>
-      <c r="G19" s="388"/>
-      <c r="H19" s="388"/>
+      <c r="G19" s="379"/>
+      <c r="H19" s="379"/>
       <c r="I19" s="141"/>
       <c r="J19" s="141"/>
       <c r="K19" s="43"/>
@@ -44781,8 +44751,8 @@
       <c r="C20" s="106"/>
       <c r="D20" s="107"/>
       <c r="F20" s="140"/>
-      <c r="G20" s="388"/>
-      <c r="H20" s="388"/>
+      <c r="G20" s="379"/>
+      <c r="H20" s="379"/>
       <c r="I20" s="141"/>
       <c r="J20" s="141"/>
       <c r="K20" s="43"/>
@@ -44796,8 +44766,8 @@
       <c r="C21" s="106"/>
       <c r="D21" s="107"/>
       <c r="F21" s="140"/>
-      <c r="G21" s="388"/>
-      <c r="H21" s="388"/>
+      <c r="G21" s="379"/>
+      <c r="H21" s="379"/>
       <c r="I21" s="140"/>
       <c r="J21" s="43"/>
       <c r="K21" s="43"/>
@@ -44822,9 +44792,9 @@
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="108"/>
-      <c r="B23" s="385"/>
-      <c r="C23" s="386"/>
-      <c r="D23" s="387"/>
+      <c r="B23" s="386"/>
+      <c r="C23" s="387"/>
+      <c r="D23" s="388"/>
       <c r="F23" s="143"/>
       <c r="G23" s="141"/>
       <c r="H23" s="141"/>
@@ -44836,10 +44806,10 @@
       <c r="N23" s="43"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="382"/>
-      <c r="B24" s="383"/>
-      <c r="C24" s="383"/>
-      <c r="D24" s="384"/>
+      <c r="A24" s="383"/>
+      <c r="B24" s="384"/>
+      <c r="C24" s="384"/>
+      <c r="D24" s="385"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
       <c r="H24" s="141"/>
@@ -44952,9 +44922,9 @@
     </row>
     <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="106"/>
-      <c r="B34" s="385"/>
-      <c r="C34" s="386"/>
-      <c r="D34" s="387"/>
+      <c r="B34" s="386"/>
+      <c r="C34" s="387"/>
+      <c r="D34" s="388"/>
       <c r="F34" s="100"/>
       <c r="I34" s="110"/>
     </row>
@@ -45087,17 +45057,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -45105,15 +45075,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
@@ -45124,6 +45085,15 @@
     <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -45374,20 +45344,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7407D7E-F487-4D85-A59A-586D8E6930DB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
     <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65D0E309-CCD4-4305-9A43-77E40C0404CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
